--- a/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7400334F-5B3E-4FDD-AE62-1D811B0D4DD4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CD7A04BB-561F-44B5-BA10-41E0FF983FF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="307">
   <si>
     <t>Symbol</t>
   </si>
@@ -62,27 +62,9 @@
     <t>Value Generation</t>
   </si>
   <si>
-    <t>Sezzle Inc.</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>2.74B</t>
-  </si>
-  <si>
-    <t>+108.40</t>
-  </si>
-  <si>
-    <t>8.97</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>-3.46</t>
-  </si>
-  <si>
     <t>Robust</t>
   </si>
   <si>
@@ -92,12 +74,6 @@
     <t>1082.KL</t>
   </si>
   <si>
-    <t>5.41B</t>
-  </si>
-  <si>
-    <t>+63.98</t>
-  </si>
-  <si>
     <t>-0.53</t>
   </si>
   <si>
@@ -113,12 +89,6 @@
     <t>VRTS</t>
   </si>
   <si>
-    <t>954.56M</t>
-  </si>
-  <si>
-    <t>+62.95</t>
-  </si>
-  <si>
     <t>0.75</t>
   </si>
   <si>
@@ -134,15 +104,6 @@
     <t>NPB</t>
   </si>
   <si>
-    <t>278.95M</t>
-  </si>
-  <si>
-    <t>+47.11</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -155,48 +116,21 @@
     <t>GCBC</t>
   </si>
   <si>
-    <t>403.54M</t>
-  </si>
-  <si>
-    <t>+47.09</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>83.31</t>
-  </si>
-  <si>
     <t>Richmond Mutual Bancorporation, Inc.</t>
   </si>
   <si>
     <t>RMBI</t>
   </si>
   <si>
-    <t>140.48M</t>
-  </si>
-  <si>
-    <t>+38.28</t>
-  </si>
-  <si>
     <t>0.17</t>
   </si>
   <si>
-    <t>-3.24</t>
-  </si>
-  <si>
     <t>Public Bank Berhad</t>
   </si>
   <si>
     <t>1295.KL</t>
   </si>
   <si>
-    <t>22.83B</t>
-  </si>
-  <si>
-    <t>+32.05</t>
-  </si>
-  <si>
     <t>-0.02</t>
   </si>
   <si>
@@ -227,12 +161,6 @@
     <t>8750.T</t>
   </si>
   <si>
-    <t>33.38B</t>
-  </si>
-  <si>
-    <t>+108.60</t>
-  </si>
-  <si>
     <t>0.32</t>
   </si>
   <si>
@@ -248,135 +176,27 @@
     <t>PYPL</t>
   </si>
   <si>
-    <t>48.73B</t>
-  </si>
-  <si>
-    <t>+62.78</t>
-  </si>
-  <si>
     <t>1.99</t>
   </si>
   <si>
     <t>-2.54</t>
   </si>
   <si>
-    <t>First United Corporation</t>
-  </si>
-  <si>
-    <t>FUNC</t>
-  </si>
-  <si>
-    <t>244.15M</t>
-  </si>
-  <si>
-    <t>+21.88</t>
-  </si>
-  <si>
-    <t>0.19</t>
-  </si>
-  <si>
-    <t>-2.49</t>
-  </si>
-  <si>
-    <t>1st Source Corporation</t>
-  </si>
-  <si>
-    <t>SRCE</t>
-  </si>
-  <si>
-    <t>1.82B</t>
-  </si>
-  <si>
-    <t>+13.32</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>-3.48</t>
-  </si>
-  <si>
-    <t>PJT Partners Inc.</t>
-  </si>
-  <si>
-    <t>PJT</t>
-  </si>
-  <si>
-    <t>4.10B</t>
-  </si>
-  <si>
-    <t>-3.19</t>
-  </si>
-  <si>
-    <t>Gentera, S.A.B. de C.V.</t>
-  </si>
-  <si>
-    <t>GENTERA.MX</t>
-  </si>
-  <si>
-    <t>4.40B</t>
-  </si>
-  <si>
-    <t>+49.73</t>
-  </si>
-  <si>
-    <t>1.90</t>
-  </si>
-  <si>
-    <t>-3.09</t>
-  </si>
-  <si>
     <t>SLM Corporation</t>
   </si>
   <si>
     <t>SLM</t>
   </si>
   <si>
-    <t>4.69B</t>
-  </si>
-  <si>
-    <t>+32.95</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>-3.01</t>
-  </si>
-  <si>
-    <t>Texas Capital Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>TCBI</t>
-  </si>
-  <si>
-    <t>4.71B</t>
-  </si>
-  <si>
-    <t>+32.39</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
     <t>9.0</t>
   </si>
   <si>
-    <t>-3.30</t>
-  </si>
-  <si>
     <t>Nelnet, Inc.</t>
   </si>
   <si>
     <t>NNI</t>
   </si>
   <si>
-    <t>5.07B</t>
-  </si>
-  <si>
-    <t>+49.25</t>
-  </si>
-  <si>
     <t>0.13</t>
   </si>
   <si>
@@ -392,153 +212,42 @@
     <t>A5G.IR</t>
   </si>
   <si>
-    <t>25.53B</t>
-  </si>
-  <si>
-    <t>+44.67</t>
-  </si>
-  <si>
     <t>0.54</t>
   </si>
   <si>
     <t>-1.84</t>
   </si>
   <si>
-    <t>Grupo Financiero Banorte, S.A.B. de C.V.</t>
-  </si>
-  <si>
-    <t>GFNORTEO.MX</t>
-  </si>
-  <si>
-    <t>31.88B</t>
-  </si>
-  <si>
-    <t>+39.73</t>
-  </si>
-  <si>
-    <t>-0.11</t>
-  </si>
-  <si>
-    <t>-4.20</t>
-  </si>
-  <si>
     <t>Bank OZK</t>
   </si>
   <si>
     <t>OZK</t>
   </si>
   <si>
-    <t>5.38B</t>
-  </si>
-  <si>
-    <t>+33.84</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
     <t>First American Financial Corporation</t>
   </si>
   <si>
     <t>FAF</t>
   </si>
   <si>
-    <t>6.82B</t>
-  </si>
-  <si>
-    <t>+69.24</t>
-  </si>
-  <si>
-    <t>1.43</t>
-  </si>
-  <si>
     <t>-2.62</t>
   </si>
   <si>
-    <t>Commerce Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>CBSH</t>
-  </si>
-  <si>
-    <t>7.10B</t>
-  </si>
-  <si>
-    <t>+25.11</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
     <t>-3.55</t>
   </si>
   <si>
-    <t>Federated Hermes, Inc.</t>
-  </si>
-  <si>
-    <t>FHI</t>
-  </si>
-  <si>
-    <t>4.26B</t>
-  </si>
-  <si>
-    <t>+15.56</t>
-  </si>
-  <si>
-    <t>5.21</t>
-  </si>
-  <si>
     <t>-2.57</t>
   </si>
   <si>
-    <t>Bupa Arabia for Cooperative Insurance Company</t>
-  </si>
-  <si>
-    <t>8210.SR</t>
-  </si>
-  <si>
-    <t>7.19B</t>
-  </si>
-  <si>
-    <t>+11.91</t>
-  </si>
-  <si>
-    <t>2.88</t>
-  </si>
-  <si>
-    <t>-2.69</t>
-  </si>
-  <si>
-    <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-  </si>
-  <si>
-    <t>MB.MI</t>
-  </si>
-  <si>
-    <t>19.78B</t>
-  </si>
-  <si>
-    <t>+36.48</t>
-  </si>
-  <si>
     <t>0.28</t>
   </si>
   <si>
-    <t>-0.55</t>
-  </si>
-  <si>
     <t>Arch Capital Group Ltd.</t>
   </si>
   <si>
     <t>ACGL</t>
   </si>
   <si>
-    <t>36.01B</t>
-  </si>
-  <si>
-    <t>+28.00</t>
-  </si>
-  <si>
     <t>1.63</t>
   </si>
   <si>
@@ -548,114 +257,18 @@
     <t>8725.T</t>
   </si>
   <si>
-    <t>37.74B</t>
-  </si>
-  <si>
-    <t>+26.86</t>
-  </si>
-  <si>
     <t>0.85</t>
   </si>
   <si>
-    <t>Mechanics Bank</t>
-  </si>
-  <si>
-    <t>MCHB</t>
-  </si>
-  <si>
-    <t>342.57K</t>
-  </si>
-  <si>
-    <t>1.11</t>
-  </si>
-  <si>
-    <t>-2.60</t>
-  </si>
-  <si>
-    <t>L1 Long Short Fund Limited</t>
-  </si>
-  <si>
-    <t>LSF.AX</t>
-  </si>
-  <si>
-    <t>1.92B</t>
-  </si>
-  <si>
-    <t>+79.72</t>
-  </si>
-  <si>
-    <t>2.43</t>
-  </si>
-  <si>
     <t>4.0</t>
   </si>
   <si>
-    <t>129.89</t>
-  </si>
-  <si>
-    <t>The Bank of Princeton</t>
-  </si>
-  <si>
-    <t>BPRN</t>
-  </si>
-  <si>
-    <t>248.13M</t>
-  </si>
-  <si>
-    <t>+26.88</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>222.23</t>
-  </si>
-  <si>
-    <t>Willis Towers Watson Public Limited Company</t>
-  </si>
-  <si>
-    <t>WTW</t>
-  </si>
-  <si>
-    <t>29.17B</t>
-  </si>
-  <si>
-    <t>+24.69</t>
-  </si>
-  <si>
-    <t>1.58</t>
-  </si>
-  <si>
-    <t>-2.27</t>
-  </si>
-  <si>
-    <t>MSCI Inc.</t>
-  </si>
-  <si>
-    <t>MSCI</t>
-  </si>
-  <si>
-    <t>43.50B</t>
-  </si>
-  <si>
-    <t>+23.55</t>
-  </si>
-  <si>
-    <t>5.99</t>
-  </si>
-  <si>
     <t>First Internet Bancorp</t>
   </si>
   <si>
     <t>INBK</t>
   </si>
   <si>
-    <t>211.44M</t>
-  </si>
-  <si>
-    <t>+17.88</t>
-  </si>
-  <si>
     <t>-0.28</t>
   </si>
   <si>
@@ -665,301 +278,685 @@
     <t>-4.16</t>
   </si>
   <si>
-    <t>Banco Latinoamericano de Comercio Exterior, S. A.</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>2.10B</t>
-  </si>
-  <si>
-    <t>+16.07</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>-4.64</t>
-  </si>
-  <si>
-    <t>Aozora Bank, Ltd.</t>
-  </si>
-  <si>
-    <t>8304.T</t>
-  </si>
-  <si>
-    <t>2.32B</t>
-  </si>
-  <si>
-    <t>+61.24</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>-3.29</t>
-  </si>
-  <si>
-    <t>Ames National Corporation</t>
-  </si>
-  <si>
-    <t>ATLO</t>
-  </si>
-  <si>
-    <t>255.74M</t>
-  </si>
-  <si>
-    <t>+14.90</t>
-  </si>
-  <si>
     <t>1.15</t>
   </si>
   <si>
-    <t>69.47</t>
-  </si>
-  <si>
     <t>NB Bancorp, Inc. Common Stock</t>
   </si>
   <si>
     <t>NBBK</t>
   </si>
   <si>
-    <t>919.60M</t>
-  </si>
-  <si>
-    <t>+51.07</t>
-  </si>
-  <si>
-    <t>1.37</t>
-  </si>
-  <si>
-    <t>306.90</t>
-  </si>
-  <si>
-    <t>Universal Insurance Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>UVE</t>
-  </si>
-  <si>
-    <t>990.94M</t>
-  </si>
-  <si>
-    <t>+32.35</t>
-  </si>
-  <si>
-    <t>2.05</t>
-  </si>
-  <si>
-    <t>-3.20</t>
-  </si>
-  <si>
-    <t>Encore Capital Group, Inc.</t>
-  </si>
-  <si>
-    <t>ECPG</t>
-  </si>
-  <si>
-    <t>1.88B</t>
-  </si>
-  <si>
-    <t>+49.19</t>
-  </si>
-  <si>
     <t>1.91</t>
   </si>
   <si>
-    <t>-2.53</t>
-  </si>
-  <si>
-    <t>CorVel Corporation</t>
-  </si>
-  <si>
-    <t>CRVL</t>
-  </si>
-  <si>
-    <t>2.88B</t>
-  </si>
-  <si>
-    <t>+54.73</t>
-  </si>
-  <si>
-    <t>12.41</t>
-  </si>
-  <si>
-    <t>-2.43</t>
-  </si>
-  <si>
-    <t>Bank of Hawaii Corporation</t>
-  </si>
-  <si>
-    <t>BOH</t>
-  </si>
-  <si>
-    <t>3.17B</t>
-  </si>
-  <si>
-    <t>+20.36</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>-3.13</t>
-  </si>
-  <si>
-    <t>Marui Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>8252.T</t>
-  </si>
-  <si>
-    <t>3.44B</t>
-  </si>
-  <si>
-    <t>+61.50</t>
-  </si>
-  <si>
-    <t>1.31</t>
-  </si>
-  <si>
-    <t>-2.17</t>
-  </si>
-  <si>
-    <t>BankUnited, Inc.</t>
-  </si>
-  <si>
-    <t>BKU</t>
-  </si>
-  <si>
-    <t>3.64B</t>
-  </si>
-  <si>
-    <t>+25.79</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>-4.26</t>
-  </si>
-  <si>
-    <t>Hilltop Holdings Inc.</t>
-  </si>
-  <si>
-    <t>HTH</t>
-  </si>
-  <si>
-    <t>2.38B</t>
-  </si>
-  <si>
-    <t>+21.55</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>-3.42</t>
-  </si>
-  <si>
-    <t>Hanmi Financial Corporation</t>
-  </si>
-  <si>
-    <t>HAFC</t>
-  </si>
-  <si>
-    <t>838.85M</t>
-  </si>
-  <si>
-    <t>+19.25</t>
-  </si>
-  <si>
-    <t>1.08</t>
-  </si>
-  <si>
-    <t>96.90</t>
-  </si>
-  <si>
-    <t>Heritage Financial Corporation</t>
-  </si>
-  <si>
-    <t>HFWA</t>
-  </si>
-  <si>
-    <t>933.51M</t>
-  </si>
-  <si>
-    <t>+17.13</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>226.86</t>
-  </si>
-  <si>
     <t>Univest Financial Corporation</t>
   </si>
   <si>
     <t>UVSP</t>
   </si>
   <si>
-    <t>1.08B</t>
-  </si>
-  <si>
-    <t>+15.35</t>
-  </si>
-  <si>
-    <t>-0.65</t>
-  </si>
-  <si>
-    <t>Skandinaviska Enskilda Banken AB (publ)</t>
-  </si>
-  <si>
-    <t>SEB-A.ST</t>
-  </si>
-  <si>
-    <t>39.96B</t>
-  </si>
-  <si>
-    <t>+14.96</t>
-  </si>
-  <si>
-    <t>-3.53</t>
-  </si>
-  <si>
-    <t>The Hartford Financial Services Group, Inc.</t>
-  </si>
-  <si>
-    <t>HIG</t>
-  </si>
-  <si>
-    <t>39.49B</t>
-  </si>
-  <si>
-    <t>+14.85</t>
-  </si>
-  <si>
-    <t>1.40</t>
-  </si>
-  <si>
-    <t>-2.39</t>
-  </si>
-  <si>
-    <t>Cathay General Bancorp</t>
-  </si>
-  <si>
-    <t>CATY</t>
-  </si>
-  <si>
-    <t>3.67B</t>
-  </si>
-  <si>
-    <t>+14.43</t>
-  </si>
-  <si>
-    <t>-0.18</t>
+    <t>48.41B</t>
+  </si>
+  <si>
+    <t>+63.85</t>
+  </si>
+  <si>
+    <t>American Integrity Insurance Group, Inc.</t>
+  </si>
+  <si>
+    <t>AII</t>
+  </si>
+  <si>
+    <t>339.02M</t>
+  </si>
+  <si>
+    <t>+40.16</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>-3.03</t>
+  </si>
+  <si>
+    <t>977.50M</t>
+  </si>
+  <si>
+    <t>+59.12</t>
+  </si>
+  <si>
+    <t>144.40M</t>
+  </si>
+  <si>
+    <t>+34.52</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>-4.77</t>
+  </si>
+  <si>
+    <t>23.39B</t>
+  </si>
+  <si>
+    <t>+28.48</t>
+  </si>
+  <si>
+    <t>398.94M</t>
+  </si>
+  <si>
+    <t>+27.57</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>-4.76</t>
+  </si>
+  <si>
+    <t>812.02M</t>
+  </si>
+  <si>
+    <t>+53.83</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>Capitol Federal Financial, Inc.</t>
+  </si>
+  <si>
+    <t>CFFN</t>
+  </si>
+  <si>
+    <t>991.65M</t>
+  </si>
+  <si>
+    <t>+39.79</t>
+  </si>
+  <si>
+    <t>33487.55</t>
+  </si>
+  <si>
+    <t>196.60M</t>
+  </si>
+  <si>
+    <t>+26.78</t>
+  </si>
+  <si>
+    <t>265.70M</t>
+  </si>
+  <si>
+    <t>+54.40</t>
+  </si>
+  <si>
+    <t>-3.79</t>
+  </si>
+  <si>
+    <t>Meridian Corporation</t>
+  </si>
+  <si>
+    <t>MRBK</t>
+  </si>
+  <si>
+    <t>217.56M</t>
+  </si>
+  <si>
+    <t>+28.34</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>204.71</t>
+  </si>
+  <si>
+    <t>Timberland Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>TSBK</t>
+  </si>
+  <si>
+    <t>320.55M</t>
+  </si>
+  <si>
+    <t>+24.85</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>176.82</t>
+  </si>
+  <si>
+    <t>1.05B</t>
+  </si>
+  <si>
+    <t>+23.80</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>-3.56</t>
+  </si>
+  <si>
+    <t>Parke Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>PKBK</t>
+  </si>
+  <si>
+    <t>351.43M</t>
+  </si>
+  <si>
+    <t>+22.52</t>
+  </si>
+  <si>
+    <t>-3.52</t>
+  </si>
+  <si>
+    <t>BayCom Corp</t>
+  </si>
+  <si>
+    <t>BCML</t>
+  </si>
+  <si>
+    <t>321.05M</t>
+  </si>
+  <si>
+    <t>+15.80</t>
+  </si>
+  <si>
+    <t>-3.47</t>
+  </si>
+  <si>
+    <t>Home Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>HBCP</t>
+  </si>
+  <si>
+    <t>479.62M</t>
+  </si>
+  <si>
+    <t>+11.51</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>-3.59</t>
+  </si>
+  <si>
+    <t>Silvercrest Asset Management Group Inc.</t>
+  </si>
+  <si>
+    <t>SAMG</t>
+  </si>
+  <si>
+    <t>117.32M</t>
+  </si>
+  <si>
+    <t>+9.85</t>
+  </si>
+  <si>
+    <t>2.67</t>
+  </si>
+  <si>
+    <t>-2.96</t>
+  </si>
+  <si>
+    <t>MainStreet Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>MNSB</t>
+  </si>
+  <si>
+    <t>178.58M</t>
+  </si>
+  <si>
+    <t>+8.17</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>-3.64</t>
+  </si>
+  <si>
+    <t>4.66B</t>
+  </si>
+  <si>
+    <t>+5.79</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>-5.13</t>
+  </si>
+  <si>
+    <t>32.12B</t>
+  </si>
+  <si>
+    <t>+115.84</t>
+  </si>
+  <si>
+    <t>First Business Financial Services, Inc.</t>
+  </si>
+  <si>
+    <t>FBIZ</t>
+  </si>
+  <si>
+    <t>458.67M</t>
+  </si>
+  <si>
+    <t>+4.96</t>
+  </si>
+  <si>
+    <t>1.28</t>
+  </si>
+  <si>
+    <t>-3.17</t>
+  </si>
+  <si>
+    <t>Morningstar, Inc.</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>7.39B</t>
+  </si>
+  <si>
+    <t>+93.32</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>FactSet Research Systems Inc.</t>
+  </si>
+  <si>
+    <t>FDS</t>
+  </si>
+  <si>
+    <t>8.33B</t>
+  </si>
+  <si>
+    <t>+78.78</t>
+  </si>
+  <si>
+    <t>3.56</t>
+  </si>
+  <si>
+    <t>-2.50</t>
+  </si>
+  <si>
+    <t>5.51B</t>
+  </si>
+  <si>
+    <t>+60.41</t>
+  </si>
+  <si>
+    <t>DNB Bank ASA</t>
+  </si>
+  <si>
+    <t>DNB.OL</t>
+  </si>
+  <si>
+    <t>43.30B</t>
+  </si>
+  <si>
+    <t>+58.56</t>
+  </si>
+  <si>
+    <t>-0.36</t>
+  </si>
+  <si>
+    <t>-3.70</t>
+  </si>
+  <si>
+    <t>Edenred SA</t>
+  </si>
+  <si>
+    <t>EDEN.PA</t>
+  </si>
+  <si>
+    <t>6.03B</t>
+  </si>
+  <si>
+    <t>+56.14</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>-3.40</t>
+  </si>
+  <si>
+    <t>South Plains Financial, Inc.</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>702.11M</t>
+  </si>
+  <si>
+    <t>+3.24</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>-2.33</t>
+  </si>
+  <si>
+    <t>24.21B</t>
+  </si>
+  <si>
+    <t>+51.92</t>
+  </si>
+  <si>
+    <t>Amerant Bancorp Inc.</t>
+  </si>
+  <si>
+    <t>AMTB</t>
+  </si>
+  <si>
+    <t>920.01M</t>
+  </si>
+  <si>
+    <t>+2.89</t>
+  </si>
+  <si>
+    <t>1.77</t>
+  </si>
+  <si>
+    <t>-5.53</t>
+  </si>
+  <si>
+    <t>7.30B</t>
+  </si>
+  <si>
+    <t>+50.99</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>Citizens Community Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>CZWI</t>
+  </si>
+  <si>
+    <t>200.25M</t>
+  </si>
+  <si>
+    <t>-7.51</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>313.54</t>
+  </si>
+  <si>
+    <t>United Cooperative Assurance Company</t>
+  </si>
+  <si>
+    <t>8190.SR</t>
+  </si>
+  <si>
+    <t>31.99M</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Al Alamiya for Cooperative Insurance Company</t>
+  </si>
+  <si>
+    <t>8280.SR</t>
+  </si>
+  <si>
+    <t>110.17M</t>
+  </si>
+  <si>
+    <t>+86.54</t>
+  </si>
+  <si>
+    <t>Resilient</t>
+  </si>
+  <si>
+    <t>Amlak International for Real Estate Finance Company</t>
+  </si>
+  <si>
+    <t>1182.SR</t>
+  </si>
+  <si>
+    <t>282.05M</t>
+  </si>
+  <si>
+    <t>+75.05</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>-3.50</t>
+  </si>
+  <si>
+    <t>Gulf Insurance Group</t>
+  </si>
+  <si>
+    <t>8250.SR</t>
+  </si>
+  <si>
+    <t>345.74M</t>
+  </si>
+  <si>
+    <t>+82.63</t>
+  </si>
+  <si>
+    <t>1.46</t>
+  </si>
+  <si>
+    <t>Sound Financial Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>SFBC</t>
+  </si>
+  <si>
+    <t>108.04M</t>
+  </si>
+  <si>
+    <t>+54.04</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>-2.63</t>
+  </si>
+  <si>
+    <t>Community West Bancshares</t>
+  </si>
+  <si>
+    <t>CWBC</t>
+  </si>
+  <si>
+    <t>461.07M</t>
+  </si>
+  <si>
+    <t>+52.34</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Midland States Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>MSBI</t>
+  </si>
+  <si>
+    <t>532.53M</t>
+  </si>
+  <si>
+    <t>+7.00</t>
+  </si>
+  <si>
+    <t>-3.34</t>
+  </si>
+  <si>
+    <t>Independent Bank Corporation</t>
+  </si>
+  <si>
+    <t>IBCP</t>
+  </si>
+  <si>
+    <t>687.81M</t>
+  </si>
+  <si>
+    <t>+3.26</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Selective Insurance Group, Inc.</t>
+  </si>
+  <si>
+    <t>SIGI</t>
+  </si>
+  <si>
+    <t>4.99B</t>
+  </si>
+  <si>
+    <t>+50.27</t>
+  </si>
+  <si>
+    <t>-12.72</t>
+  </si>
+  <si>
+    <t>5.13B</t>
+  </si>
+  <si>
+    <t>+47.45</t>
+  </si>
+  <si>
+    <t>5.25B</t>
+  </si>
+  <si>
+    <t>+33.37</t>
+  </si>
+  <si>
+    <t>-3.68</t>
+  </si>
+  <si>
+    <t>36.57B</t>
+  </si>
+  <si>
+    <t>+30.37</t>
+  </si>
+  <si>
+    <t>Amundi S.A.</t>
+  </si>
+  <si>
+    <t>AMUN.PA</t>
+  </si>
+  <si>
+    <t>18.42B</t>
+  </si>
+  <si>
+    <t>+29.98</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>-4.25</t>
+  </si>
+  <si>
+    <t>35.49B</t>
+  </si>
+  <si>
+    <t>+29.87</t>
+  </si>
+  <si>
+    <t>Quálitas Controladora, S.A.B. de C.V.</t>
+  </si>
+  <si>
+    <t>Q.MX</t>
+  </si>
+  <si>
+    <t>4.14B</t>
+  </si>
+  <si>
+    <t>+23.95</t>
+  </si>
+  <si>
+    <t>1.56</t>
+  </si>
+  <si>
+    <t>-7.14</t>
+  </si>
+  <si>
+    <t>Principal Financial Group, Inc.</t>
+  </si>
+  <si>
+    <t>PFG</t>
+  </si>
+  <si>
+    <t>21.88B</t>
+  </si>
+  <si>
+    <t>-3.04</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>-4.57</t>
+  </si>
+  <si>
+    <t>Northeast Community Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>NECB</t>
+  </si>
+  <si>
+    <t>322.11M</t>
+  </si>
+  <si>
+    <t>+35.73</t>
+  </si>
+  <si>
+    <t>-2.67</t>
+  </si>
+  <si>
+    <t>Landmark Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>LARK</t>
+  </si>
+  <si>
+    <t>163.91M</t>
+  </si>
+  <si>
+    <t>+29.15</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>-3.61</t>
   </si>
 </sst>
 </file>
@@ -1335,12 +1332,12 @@
   <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="48.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1375,36 +1372,36 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1412,36 +1409,36 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1449,36 +1446,36 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1486,36 +1483,36 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1523,36 +1520,36 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1560,36 +1557,36 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1597,36 +1594,36 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1634,36 +1631,36 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1671,36 +1668,36 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,36 +1705,36 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1745,36 +1742,36 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1782,36 +1779,36 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1819,36 +1816,36 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1856,36 +1853,36 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H28" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I28" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1893,36 +1890,36 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1930,36 +1927,36 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1967,36 +1964,36 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2004,36 +2001,36 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F36" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G36" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H36" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="I36" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2041,36 +2038,36 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="F38" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="H38" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2078,36 +2075,36 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="G40" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="H40" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="J40" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2115,36 +2112,36 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="E42" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="J42" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>134</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2152,36 +2149,36 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="F44" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="G44" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="I44" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="J44" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,36 +2186,36 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="J46" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2226,36 +2223,36 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="F48" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="H48" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="J48" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2263,36 +2260,36 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="I50" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="J50" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2300,36 +2297,36 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C52" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E52" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="F52" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="G52" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="I52" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="J52" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2337,36 +2334,36 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="E54" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="G54" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="H54" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="J54" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2374,36 +2371,36 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="D56" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="G56" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="H56" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="J56" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2411,36 +2408,36 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="G58" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="H58" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="I58" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="J58" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2448,36 +2445,36 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C60" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="D60" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F60" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="G60" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="H60" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I60" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="J60" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2485,36 +2482,36 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="F62" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="G62" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="H62" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="J62" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>192</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -2522,36 +2519,36 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C64" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="D64" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="E64" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="F64" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G64" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="H64" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="J64" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2559,36 +2556,36 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C66" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D66" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="G66" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="I66" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="J66" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2596,36 +2593,36 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C68" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D68" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="F68" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="G68" t="s">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="H68" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>214</v>
+        <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2633,36 +2630,36 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D70" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="F70" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G70" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="H70" t="s">
-        <v>207</v>
+        <v>54</v>
       </c>
       <c r="I70" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="J70" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2670,36 +2667,36 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C72" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D72" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="F72" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G72" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="H72" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="J72" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2707,36 +2704,36 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C74" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="D74" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E74" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="F74" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="G74" t="s">
+        <v>247</v>
+      </c>
+      <c r="H74" t="s">
+        <v>78</v>
+      </c>
+      <c r="I74" t="s">
+        <v>248</v>
+      </c>
+      <c r="J74" t="s">
         <v>231</v>
-      </c>
-      <c r="H74" t="s">
-        <v>66</v>
-      </c>
-      <c r="I74" t="s">
-        <v>232</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -2744,36 +2741,36 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C76" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F76" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="G76" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I76" t="s">
-        <v>238</v>
+        <v>65</v>
       </c>
       <c r="J76" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -2781,36 +2778,36 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="C78" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="E78" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="F78" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="G78" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="H78" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I78" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="J78" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2818,36 +2815,36 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D80" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="F80" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G80" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="H80" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="J80" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2855,36 +2852,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D82" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="E82" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I82" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="J82" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -2892,36 +2889,36 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="D84" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E84" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="F84" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G84" t="s">
-        <v>261</v>
+        <v>53</v>
       </c>
       <c r="H84" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="I84" t="s">
-        <v>262</v>
+        <v>55</v>
       </c>
       <c r="J84" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -2929,36 +2926,36 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E86" t="s">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="F86" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G86" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="I86" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J86" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>264</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -2966,36 +2963,36 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="D88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E88" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="F88" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G88" t="s">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>274</v>
+        <v>65</v>
       </c>
       <c r="J88" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>270</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3003,36 +3000,36 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F90" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H90" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J90" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3040,36 +3037,36 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>281</v>
+        <v>68</v>
       </c>
       <c r="D92" t="s">
+        <v>282</v>
+      </c>
+      <c r="E92" t="s">
+        <v>68</v>
+      </c>
+      <c r="F92" t="s">
         <v>283</v>
       </c>
-      <c r="E92" t="s">
-        <v>281</v>
-      </c>
-      <c r="F92" t="s">
-        <v>284</v>
-      </c>
       <c r="G92" t="s">
-        <v>285</v>
+        <v>70</v>
       </c>
       <c r="H92" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>286</v>
+        <v>64</v>
       </c>
       <c r="J92" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>282</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3077,36 +3074,36 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
+        <v>284</v>
+      </c>
+      <c r="C94" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" t="s">
+        <v>286</v>
+      </c>
+      <c r="E94" t="s">
+        <v>284</v>
+      </c>
+      <c r="F94" t="s">
         <v>287</v>
       </c>
-      <c r="C94" t="s">
-        <v>287</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="G94" t="s">
+        <v>288</v>
+      </c>
+      <c r="H94" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" t="s">
         <v>289</v>
       </c>
-      <c r="E94" t="s">
-        <v>287</v>
-      </c>
-      <c r="F94" t="s">
-        <v>290</v>
-      </c>
-      <c r="G94" t="s">
-        <v>291</v>
-      </c>
-      <c r="H94" t="s">
-        <v>114</v>
-      </c>
-      <c r="I94" t="s">
-        <v>238</v>
-      </c>
       <c r="J94" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3114,36 +3111,36 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
+        <v>290</v>
+      </c>
+      <c r="C96" t="s">
+        <v>290</v>
+      </c>
+      <c r="D96" t="s">
         <v>292</v>
       </c>
-      <c r="C96" t="s">
-        <v>292</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>290</v>
+      </c>
+      <c r="F96" t="s">
+        <v>293</v>
+      </c>
+      <c r="G96" t="s">
         <v>294</v>
       </c>
-      <c r="E96" t="s">
-        <v>292</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
         <v>295</v>
       </c>
-      <c r="G96" t="s">
-        <v>206</v>
-      </c>
-      <c r="H96" t="s">
-        <v>28</v>
-      </c>
-      <c r="I96" t="s">
-        <v>296</v>
-      </c>
       <c r="J96" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3151,36 +3148,36 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D98" t="s">
+        <v>298</v>
+      </c>
+      <c r="E98" t="s">
+        <v>296</v>
+      </c>
+      <c r="F98" t="s">
         <v>299</v>
       </c>
-      <c r="E98" t="s">
-        <v>297</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
+        <v>133</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
         <v>300</v>
       </c>
-      <c r="G98" t="s">
-        <v>301</v>
-      </c>
-      <c r="H98" t="s">
-        <v>107</v>
-      </c>
-      <c r="I98" t="s">
-        <v>302</v>
-      </c>
       <c r="J98" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3188,36 +3185,36 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
+        <v>301</v>
+      </c>
+      <c r="C100" t="s">
+        <v>301</v>
+      </c>
+      <c r="D100" t="s">
         <v>303</v>
       </c>
-      <c r="C100" t="s">
-        <v>303</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>301</v>
+      </c>
+      <c r="F100" t="s">
+        <v>304</v>
+      </c>
+      <c r="G100" t="s">
         <v>305</v>
       </c>
-      <c r="E100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
         <v>306</v>
       </c>
-      <c r="G100" t="s">
-        <v>307</v>
-      </c>
-      <c r="H100" t="s">
-        <v>13</v>
-      </c>
-      <c r="I100" t="s">
-        <v>244</v>
-      </c>
       <c r="J100" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7400334F-5B3E-4FDD-AE62-1D811B0D4DD4}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{273AE238-3077-4F10-A66D-9A234204C7FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CD7A04BB-561F-44B5-BA10-41E0FF983FF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="302">
   <si>
     <t>Symbol</t>
   </si>
@@ -68,21 +68,6 @@
     <t>Robust</t>
   </si>
   <si>
-    <t>Hong Leong Financial Group Berhad</t>
-  </si>
-  <si>
-    <t>1082.KL</t>
-  </si>
-  <si>
-    <t>-0.53</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>-4.02</t>
-  </si>
-  <si>
     <t>Virtus Investment Partners, Inc.</t>
   </si>
   <si>
@@ -125,141 +110,30 @@
     <t>0.17</t>
   </si>
   <si>
-    <t>Public Bank Berhad</t>
-  </si>
-  <si>
-    <t>1295.KL</t>
-  </si>
-  <si>
-    <t>-0.02</t>
-  </si>
-  <si>
-    <t>-4.42</t>
-  </si>
-  <si>
-    <t>Blue Foundry Bancorp</t>
-  </si>
-  <si>
-    <t>BLFY</t>
-  </si>
-  <si>
-    <t>260.12M</t>
-  </si>
-  <si>
-    <t>+28.32</t>
-  </si>
-  <si>
-    <t>1.33</t>
-  </si>
-  <si>
-    <t>-5.15</t>
-  </si>
-  <si>
-    <t>Dai-ichi Life Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>8750.T</t>
-  </si>
-  <si>
     <t>0.32</t>
   </si>
   <si>
     <t>5.0</t>
   </si>
   <si>
-    <t>-3.35</t>
-  </si>
-  <si>
-    <t>PayPal Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>1.99</t>
-  </si>
-  <si>
-    <t>-2.54</t>
-  </si>
-  <si>
-    <t>SLM Corporation</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
     <t>9.0</t>
   </si>
   <si>
-    <t>Nelnet, Inc.</t>
-  </si>
-  <si>
-    <t>NNI</t>
-  </si>
-  <si>
     <t>0.13</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>-2.87</t>
-  </si>
-  <si>
-    <t>AIB Group plc</t>
-  </si>
-  <si>
-    <t>A5G.IR</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>-1.84</t>
-  </si>
-  <si>
-    <t>Bank OZK</t>
-  </si>
-  <si>
-    <t>OZK</t>
-  </si>
-  <si>
-    <t>First American Financial Corporation</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
     <t>-2.62</t>
   </si>
   <si>
     <t>-3.55</t>
   </si>
   <si>
-    <t>-2.57</t>
-  </si>
-  <si>
     <t>0.28</t>
   </si>
   <si>
-    <t>Arch Capital Group Ltd.</t>
-  </si>
-  <si>
-    <t>ACGL</t>
-  </si>
-  <si>
-    <t>1.63</t>
-  </si>
-  <si>
-    <t>MS&amp;AD Insurance Group Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>8725.T</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
     <t>4.0</t>
   </si>
   <si>
@@ -269,129 +143,48 @@
     <t>INBK</t>
   </si>
   <si>
-    <t>-0.28</t>
-  </si>
-  <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>-4.16</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
     <t>NB Bancorp, Inc. Common Stock</t>
   </si>
   <si>
     <t>NBBK</t>
   </si>
   <si>
-    <t>1.91</t>
-  </si>
-  <si>
     <t>Univest Financial Corporation</t>
   </si>
   <si>
     <t>UVSP</t>
   </si>
   <si>
-    <t>48.41B</t>
-  </si>
-  <si>
-    <t>+63.85</t>
-  </si>
-  <si>
     <t>American Integrity Insurance Group, Inc.</t>
   </si>
   <si>
     <t>AII</t>
   </si>
   <si>
-    <t>339.02M</t>
-  </si>
-  <si>
-    <t>+40.16</t>
-  </si>
-  <si>
     <t>0.97</t>
   </si>
   <si>
     <t>-3.03</t>
   </si>
   <si>
-    <t>977.50M</t>
-  </si>
-  <si>
-    <t>+59.12</t>
-  </si>
-  <si>
-    <t>144.40M</t>
-  </si>
-  <si>
-    <t>+34.52</t>
-  </si>
-  <si>
     <t>0.15</t>
   </si>
   <si>
     <t>-4.77</t>
   </si>
   <si>
-    <t>23.39B</t>
-  </si>
-  <si>
-    <t>+28.48</t>
-  </si>
-  <si>
-    <t>398.94M</t>
-  </si>
-  <si>
-    <t>+27.57</t>
-  </si>
-  <si>
     <t>0.84</t>
   </si>
   <si>
     <t>-4.76</t>
   </si>
   <si>
-    <t>812.02M</t>
-  </si>
-  <si>
-    <t>+53.83</t>
-  </si>
-  <si>
     <t>1.38</t>
   </si>
   <si>
-    <t>Capitol Federal Financial, Inc.</t>
-  </si>
-  <si>
-    <t>CFFN</t>
-  </si>
-  <si>
-    <t>991.65M</t>
-  </si>
-  <si>
-    <t>+39.79</t>
-  </si>
-  <si>
-    <t>33487.55</t>
-  </si>
-  <si>
-    <t>196.60M</t>
-  </si>
-  <si>
-    <t>+26.78</t>
-  </si>
-  <si>
-    <t>265.70M</t>
-  </si>
-  <si>
-    <t>+54.40</t>
-  </si>
-  <si>
     <t>-3.79</t>
   </si>
   <si>
@@ -401,12 +194,6 @@
     <t>MRBK</t>
   </si>
   <si>
-    <t>217.56M</t>
-  </si>
-  <si>
-    <t>+28.34</t>
-  </si>
-  <si>
     <t>0.26</t>
   </si>
   <si>
@@ -419,24 +206,9 @@
     <t>TSBK</t>
   </si>
   <si>
-    <t>320.55M</t>
-  </si>
-  <si>
-    <t>+24.85</t>
-  </si>
-  <si>
     <t>1.35</t>
   </si>
   <si>
-    <t>176.82</t>
-  </si>
-  <si>
-    <t>1.05B</t>
-  </si>
-  <si>
-    <t>+23.80</t>
-  </si>
-  <si>
     <t>0.30</t>
   </si>
   <si>
@@ -449,12 +221,6 @@
     <t>PKBK</t>
   </si>
   <si>
-    <t>351.43M</t>
-  </si>
-  <si>
-    <t>+22.52</t>
-  </si>
-  <si>
     <t>-3.52</t>
   </si>
   <si>
@@ -464,12 +230,6 @@
     <t>BCML</t>
   </si>
   <si>
-    <t>321.05M</t>
-  </si>
-  <si>
-    <t>+15.80</t>
-  </si>
-  <si>
     <t>-3.47</t>
   </si>
   <si>
@@ -479,12 +239,6 @@
     <t>HBCP</t>
   </si>
   <si>
-    <t>479.62M</t>
-  </si>
-  <si>
-    <t>+11.51</t>
-  </si>
-  <si>
     <t>0.51</t>
   </si>
   <si>
@@ -497,12 +251,6 @@
     <t>SAMG</t>
   </si>
   <si>
-    <t>117.32M</t>
-  </si>
-  <si>
-    <t>+9.85</t>
-  </si>
-  <si>
     <t>2.67</t>
   </si>
   <si>
@@ -515,222 +263,72 @@
     <t>MNSB</t>
   </si>
   <si>
-    <t>178.58M</t>
-  </si>
-  <si>
-    <t>+8.17</t>
-  </si>
-  <si>
     <t>0.25</t>
   </si>
   <si>
     <t>-3.64</t>
   </si>
   <si>
-    <t>4.66B</t>
-  </si>
-  <si>
-    <t>+5.79</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>-5.13</t>
-  </si>
-  <si>
-    <t>32.12B</t>
-  </si>
-  <si>
-    <t>+115.84</t>
-  </si>
-  <si>
     <t>First Business Financial Services, Inc.</t>
   </si>
   <si>
     <t>FBIZ</t>
   </si>
   <si>
-    <t>458.67M</t>
-  </si>
-  <si>
-    <t>+4.96</t>
-  </si>
-  <si>
     <t>1.28</t>
   </si>
   <si>
     <t>-3.17</t>
   </si>
   <si>
-    <t>Morningstar, Inc.</t>
-  </si>
-  <si>
-    <t>MORN</t>
-  </si>
-  <si>
-    <t>7.39B</t>
-  </si>
-  <si>
-    <t>+93.32</t>
-  </si>
-  <si>
-    <t>4.33</t>
-  </si>
-  <si>
     <t>FactSet Research Systems Inc.</t>
   </si>
   <si>
     <t>FDS</t>
   </si>
   <si>
-    <t>8.33B</t>
-  </si>
-  <si>
-    <t>+78.78</t>
-  </si>
-  <si>
     <t>3.56</t>
   </si>
   <si>
     <t>-2.50</t>
   </si>
   <si>
-    <t>5.51B</t>
-  </si>
-  <si>
-    <t>+60.41</t>
-  </si>
-  <si>
-    <t>DNB Bank ASA</t>
-  </si>
-  <si>
-    <t>DNB.OL</t>
-  </si>
-  <si>
-    <t>43.30B</t>
-  </si>
-  <si>
-    <t>+58.56</t>
-  </si>
-  <si>
-    <t>-0.36</t>
-  </si>
-  <si>
-    <t>-3.70</t>
-  </si>
-  <si>
-    <t>Edenred SA</t>
-  </si>
-  <si>
-    <t>EDEN.PA</t>
-  </si>
-  <si>
-    <t>6.03B</t>
-  </si>
-  <si>
-    <t>+56.14</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>-3.40</t>
-  </si>
-  <si>
     <t>South Plains Financial, Inc.</t>
   </si>
   <si>
     <t>SPFI</t>
   </si>
   <si>
-    <t>702.11M</t>
-  </si>
-  <si>
-    <t>+3.24</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>-2.33</t>
-  </si>
-  <si>
-    <t>24.21B</t>
-  </si>
-  <si>
-    <t>+51.92</t>
-  </si>
-  <si>
     <t>Amerant Bancorp Inc.</t>
   </si>
   <si>
     <t>AMTB</t>
   </si>
   <si>
-    <t>920.01M</t>
-  </si>
-  <si>
-    <t>+2.89</t>
-  </si>
-  <si>
     <t>1.77</t>
   </si>
   <si>
     <t>-5.53</t>
   </si>
   <si>
-    <t>7.30B</t>
-  </si>
-  <si>
-    <t>+50.99</t>
-  </si>
-  <si>
-    <t>1.03</t>
-  </si>
-  <si>
     <t>Citizens Community Bancorp, Inc.</t>
   </si>
   <si>
     <t>CZWI</t>
   </si>
   <si>
-    <t>200.25M</t>
-  </si>
-  <si>
-    <t>-7.51</t>
-  </si>
-  <si>
-    <t>1.26</t>
-  </si>
-  <si>
-    <t>313.54</t>
-  </si>
-  <si>
     <t>United Cooperative Assurance Company</t>
   </si>
   <si>
     <t>8190.SR</t>
   </si>
   <si>
-    <t>31.99M</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
     <t>Al Alamiya for Cooperative Insurance Company</t>
   </si>
   <si>
     <t>8280.SR</t>
   </si>
   <si>
-    <t>110.17M</t>
-  </si>
-  <si>
-    <t>+86.54</t>
-  </si>
-  <si>
     <t>Resilient</t>
   </si>
   <si>
@@ -740,63 +338,24 @@
     <t>1182.SR</t>
   </si>
   <si>
-    <t>282.05M</t>
-  </si>
-  <si>
-    <t>+75.05</t>
-  </si>
-  <si>
     <t>0.63</t>
   </si>
   <si>
     <t>-3.50</t>
   </si>
   <si>
-    <t>Gulf Insurance Group</t>
-  </si>
-  <si>
-    <t>8250.SR</t>
-  </si>
-  <si>
-    <t>345.74M</t>
-  </si>
-  <si>
-    <t>+82.63</t>
-  </si>
-  <si>
-    <t>1.46</t>
-  </si>
-  <si>
     <t>Sound Financial Bancorp, Inc.</t>
   </si>
   <si>
     <t>SFBC</t>
   </si>
   <si>
-    <t>108.04M</t>
-  </si>
-  <si>
-    <t>+54.04</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>-2.63</t>
-  </si>
-  <si>
     <t>Community West Bancshares</t>
   </si>
   <si>
     <t>CWBC</t>
   </si>
   <si>
-    <t>461.07M</t>
-  </si>
-  <si>
-    <t>+52.34</t>
-  </si>
-  <si>
     <t>0.43</t>
   </si>
   <si>
@@ -806,12 +365,6 @@
     <t>MSBI</t>
   </si>
   <si>
-    <t>532.53M</t>
-  </si>
-  <si>
-    <t>+7.00</t>
-  </si>
-  <si>
     <t>-3.34</t>
   </si>
   <si>
@@ -821,142 +374,574 @@
     <t>IBCP</t>
   </si>
   <si>
-    <t>687.81M</t>
-  </si>
-  <si>
-    <t>+3.26</t>
-  </si>
-  <si>
     <t>0.34</t>
   </si>
   <si>
-    <t>Selective Insurance Group, Inc.</t>
-  </si>
-  <si>
-    <t>SIGI</t>
-  </si>
-  <si>
-    <t>4.99B</t>
-  </si>
-  <si>
-    <t>+50.27</t>
-  </si>
-  <si>
-    <t>-12.72</t>
-  </si>
-  <si>
-    <t>5.13B</t>
-  </si>
-  <si>
-    <t>+47.45</t>
-  </si>
-  <si>
-    <t>5.25B</t>
-  </si>
-  <si>
-    <t>+33.37</t>
-  </si>
-  <si>
-    <t>-3.68</t>
-  </si>
-  <si>
-    <t>36.57B</t>
-  </si>
-  <si>
-    <t>+30.37</t>
-  </si>
-  <si>
-    <t>Amundi S.A.</t>
-  </si>
-  <si>
-    <t>AMUN.PA</t>
-  </si>
-  <si>
-    <t>18.42B</t>
-  </si>
-  <si>
-    <t>+29.98</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
     <t>-4.25</t>
   </si>
   <si>
-    <t>35.49B</t>
-  </si>
-  <si>
-    <t>+29.87</t>
-  </si>
-  <si>
-    <t>Quálitas Controladora, S.A.B. de C.V.</t>
-  </si>
-  <si>
-    <t>Q.MX</t>
-  </si>
-  <si>
-    <t>4.14B</t>
-  </si>
-  <si>
-    <t>+23.95</t>
-  </si>
-  <si>
-    <t>1.56</t>
-  </si>
-  <si>
-    <t>-7.14</t>
-  </si>
-  <si>
-    <t>Principal Financial Group, Inc.</t>
-  </si>
-  <si>
-    <t>PFG</t>
-  </si>
-  <si>
-    <t>21.88B</t>
-  </si>
-  <si>
-    <t>-3.04</t>
-  </si>
-  <si>
     <t>0.18</t>
   </si>
   <si>
-    <t>-4.57</t>
-  </si>
-  <si>
-    <t>Northeast Community Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>NECB</t>
-  </si>
-  <si>
-    <t>322.11M</t>
-  </si>
-  <si>
-    <t>+35.73</t>
-  </si>
-  <si>
-    <t>-2.67</t>
-  </si>
-  <si>
     <t>Landmark Bancorp, Inc.</t>
   </si>
   <si>
     <t>LARK</t>
   </si>
   <si>
-    <t>163.91M</t>
-  </si>
-  <si>
-    <t>+29.15</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>-3.61</t>
+    <t>PRA Group, Inc.</t>
+  </si>
+  <si>
+    <t>PRAA</t>
+  </si>
+  <si>
+    <t>866.51M</t>
+  </si>
+  <si>
+    <t>+234.27</t>
+  </si>
+  <si>
+    <t>8.65B</t>
+  </si>
+  <si>
+    <t>+74.50</t>
+  </si>
+  <si>
+    <t>960.50M</t>
+  </si>
+  <si>
+    <t>+65.45</t>
+  </si>
+  <si>
+    <t>266.98M</t>
+  </si>
+  <si>
+    <t>+54.62</t>
+  </si>
+  <si>
+    <t>339.36M</t>
+  </si>
+  <si>
+    <t>+40.73</t>
+  </si>
+  <si>
+    <t>311.08M</t>
+  </si>
+  <si>
+    <t>+29.49</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>410.43M</t>
+  </si>
+  <si>
+    <t>+27.40</t>
+  </si>
+  <si>
+    <t>801.57M</t>
+  </si>
+  <si>
+    <t>+51.96</t>
+  </si>
+  <si>
+    <t>Southside Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>SBSI</t>
+  </si>
+  <si>
+    <t>998.44M</t>
+  </si>
+  <si>
+    <t>+32.69</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>-3.24</t>
+  </si>
+  <si>
+    <t>1.04B</t>
+  </si>
+  <si>
+    <t>+29.80</t>
+  </si>
+  <si>
+    <t>221.63M</t>
+  </si>
+  <si>
+    <t>+25.45</t>
+  </si>
+  <si>
+    <t>351.61M</t>
+  </si>
+  <si>
+    <t>+25.29</t>
+  </si>
+  <si>
+    <t>322.91M</t>
+  </si>
+  <si>
+    <t>+15.24</t>
+  </si>
+  <si>
+    <t>174.46M</t>
+  </si>
+  <si>
+    <t>+12.87</t>
+  </si>
+  <si>
+    <t>479.93M</t>
+  </si>
+  <si>
+    <t>+12.44</t>
+  </si>
+  <si>
+    <t>114.87M</t>
+  </si>
+  <si>
+    <t>+10.90</t>
+  </si>
+  <si>
+    <t>553.62M</t>
+  </si>
+  <si>
+    <t>+9.54</t>
+  </si>
+  <si>
+    <t>465.92M</t>
+  </si>
+  <si>
+    <t>+5.10</t>
+  </si>
+  <si>
+    <t>679.58M</t>
+  </si>
+  <si>
+    <t>+4.24</t>
+  </si>
+  <si>
+    <t>152.53M</t>
+  </si>
+  <si>
+    <t>-0.25</t>
+  </si>
+  <si>
+    <t>670.61M</t>
+  </si>
+  <si>
+    <t>-1.47</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>198.99M</t>
+  </si>
+  <si>
+    <t>-2.15</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>-2.73</t>
+  </si>
+  <si>
+    <t>Red River Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>RRBI</t>
+  </si>
+  <si>
+    <t>590.94M</t>
+  </si>
+  <si>
+    <t>-7.45</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Ames National Corporation</t>
+  </si>
+  <si>
+    <t>ATLO</t>
+  </si>
+  <si>
+    <t>251.19M</t>
+  </si>
+  <si>
+    <t>-16.91</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>-2.61</t>
+  </si>
+  <si>
+    <t>31.78M</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>-3.15</t>
+  </si>
+  <si>
+    <t>202.70M</t>
+  </si>
+  <si>
+    <t>-65.37</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>-2.75</t>
+  </si>
+  <si>
+    <t>Donegal Group Inc.</t>
+  </si>
+  <si>
+    <t>DGICA</t>
+  </si>
+  <si>
+    <t>521.08M</t>
+  </si>
+  <si>
+    <t>+159.29</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>-3.67</t>
+  </si>
+  <si>
+    <t>104.89M</t>
+  </si>
+  <si>
+    <t>+102.75</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>11.54</t>
+  </si>
+  <si>
+    <t>108.47M</t>
+  </si>
+  <si>
+    <t>+89.28</t>
+  </si>
+  <si>
+    <t>451.72M</t>
+  </si>
+  <si>
+    <t>+56.16</t>
+  </si>
+  <si>
+    <t>159.38M</t>
+  </si>
+  <si>
+    <t>+23.24</t>
+  </si>
+  <si>
+    <t>Westwood Holdings Group, Inc.</t>
+  </si>
+  <si>
+    <t>WHG</t>
+  </si>
+  <si>
+    <t>142.26M</t>
+  </si>
+  <si>
+    <t>+23.00</t>
+  </si>
+  <si>
+    <t>4.70</t>
+  </si>
+  <si>
+    <t>-2.69</t>
+  </si>
+  <si>
+    <t>Saudi Arabian Cooperative Insurance Company</t>
+  </si>
+  <si>
+    <t>8100.SR</t>
+  </si>
+  <si>
+    <t>69.35M</t>
+  </si>
+  <si>
+    <t>+20.18</t>
+  </si>
+  <si>
+    <t>1.76</t>
+  </si>
+  <si>
+    <t>Chubb Arabia Cooperative Insurance Company</t>
+  </si>
+  <si>
+    <t>8240.SR</t>
+  </si>
+  <si>
+    <t>194.18M</t>
+  </si>
+  <si>
+    <t>+51.30</t>
+  </si>
+  <si>
+    <t>2.99</t>
+  </si>
+  <si>
+    <t>-2.46</t>
+  </si>
+  <si>
+    <t>LCNB Corp.</t>
+  </si>
+  <si>
+    <t>LCNB</t>
+  </si>
+  <si>
+    <t>226.64M</t>
+  </si>
+  <si>
+    <t>+40.11</t>
+  </si>
+  <si>
+    <t>Fidelity D &amp; D Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>FDBC</t>
+  </si>
+  <si>
+    <t>260.74M</t>
+  </si>
+  <si>
+    <t>+19.17</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>-4.41</t>
+  </si>
+  <si>
+    <t>Western New England Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>WNEB</t>
+  </si>
+  <si>
+    <t>277.35M</t>
+  </si>
+  <si>
+    <t>+2.81</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>286.70M</t>
+  </si>
+  <si>
+    <t>+73.65</t>
+  </si>
+  <si>
+    <t>First United Corporation</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>240.32M</t>
+  </si>
+  <si>
+    <t>-13.42</t>
+  </si>
+  <si>
+    <t>-4.75</t>
+  </si>
+  <si>
+    <t>Southern California Bancorp</t>
+  </si>
+  <si>
+    <t>BCAL</t>
+  </si>
+  <si>
+    <t>607.77M</t>
+  </si>
+  <si>
+    <t>+91.83</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>-3.46</t>
+  </si>
+  <si>
+    <t>Hawthorn Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>HWBK</t>
+  </si>
+  <si>
+    <t>232.79M</t>
+  </si>
+  <si>
+    <t>+242.53</t>
+  </si>
+  <si>
+    <t>-3.44</t>
+  </si>
+  <si>
+    <t>Steady</t>
+  </si>
+  <si>
+    <t>LINKBANCORP, Inc.</t>
+  </si>
+  <si>
+    <t>LNKB</t>
+  </si>
+  <si>
+    <t>323.85M</t>
+  </si>
+  <si>
+    <t>+63.98</t>
+  </si>
+  <si>
+    <t>-0.70</t>
+  </si>
+  <si>
+    <t>-3.28</t>
+  </si>
+  <si>
+    <t>NZX Limited</t>
+  </si>
+  <si>
+    <t>NZX.NZ</t>
+  </si>
+  <si>
+    <t>271.02M</t>
+  </si>
+  <si>
+    <t>+37.14</t>
+  </si>
+  <si>
+    <t>3.04</t>
+  </si>
+  <si>
+    <t>LendingTree, Inc.</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>565.13M</t>
+  </si>
+  <si>
+    <t>+35.52</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>-2.59</t>
+  </si>
+  <si>
+    <t>C&amp;F Financial Corporation</t>
+  </si>
+  <si>
+    <t>CFFI</t>
+  </si>
+  <si>
+    <t>249.06M</t>
+  </si>
+  <si>
+    <t>+34.80</t>
+  </si>
+  <si>
+    <t>-3.19</t>
+  </si>
+  <si>
+    <t>USCB Financial Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>USCB</t>
+  </si>
+  <si>
+    <t>333.52M</t>
+  </si>
+  <si>
+    <t>+33.81</t>
+  </si>
+  <si>
+    <t>-4.34</t>
+  </si>
+  <si>
+    <t>Employers Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>EIG</t>
+  </si>
+  <si>
+    <t>1.02B</t>
+  </si>
+  <si>
+    <t>+22.50</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>Heritage Financial Corporation</t>
+  </si>
+  <si>
+    <t>HFWA</t>
+  </si>
+  <si>
+    <t>1.06B</t>
+  </si>
+  <si>
+    <t>+8.71</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>-2.42</t>
+  </si>
+  <si>
+    <t>Hanmi Financial Corporation</t>
+  </si>
+  <si>
+    <t>HAFC</t>
+  </si>
+  <si>
+    <t>892.13M</t>
+  </si>
+  <si>
+    <t>+5.85</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>7.22</t>
+  </si>
+  <si>
+    <t>920.81M</t>
+  </si>
+  <si>
+    <t>+4.16</t>
   </si>
 </sst>
 </file>
@@ -1009,6 +994,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1372,28 +1361,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
         <v>9</v>
@@ -1401,7 +1390,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1409,28 +1398,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="J4" t="s">
         <v>9</v>
@@ -1438,7 +1427,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1446,28 +1435,28 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>9</v>
@@ -1475,7 +1464,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1483,28 +1472,28 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
         <v>9</v>
@@ -1512,7 +1501,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1520,28 +1509,28 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
@@ -1549,7 +1538,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1557,28 +1546,28 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="J12" t="s">
         <v>9</v>
@@ -1586,7 +1575,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1594,28 +1583,28 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
         <v>9</v>
@@ -1623,7 +1612,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1631,28 +1620,28 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="J16" t="s">
         <v>9</v>
@@ -1660,7 +1649,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1668,28 +1657,28 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H18" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I18" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="J18" t="s">
         <v>9</v>
@@ -1697,7 +1686,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1705,28 +1694,28 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J20" t="s">
         <v>9</v>
@@ -1734,7 +1723,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1742,28 +1731,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="J22" t="s">
         <v>9</v>
@@ -1771,7 +1760,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1779,28 +1768,28 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
         <v>9</v>
@@ -1808,7 +1797,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1816,28 +1805,28 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -1845,7 +1834,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1853,28 +1842,28 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="J28" t="s">
         <v>9</v>
@@ -1882,7 +1871,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1890,28 +1879,28 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="H30" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="J30" t="s">
         <v>9</v>
@@ -1919,7 +1908,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1927,28 +1916,28 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E32" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" t="s">
         <v>28</v>
       </c>
-      <c r="H32" t="s">
-        <v>54</v>
-      </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="J32" t="s">
         <v>9</v>
@@ -1956,7 +1945,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1964,28 +1953,28 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G34" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="J34" t="s">
         <v>9</v>
@@ -1993,7 +1982,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2001,28 +1990,28 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G36" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s">
         <v>9</v>
@@ -2030,7 +2019,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2038,28 +2027,28 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="F38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G38" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I38" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
@@ -2067,7 +2056,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2075,28 +2064,28 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
         <v>163</v>
       </c>
-      <c r="E40" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" t="s">
-        <v>164</v>
-      </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I40" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="J40" t="s">
         <v>9</v>
@@ -2104,7 +2093,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2112,28 +2101,28 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I42" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -2141,7 +2130,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2149,28 +2138,28 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" t="s">
+        <v>168</v>
+      </c>
+      <c r="G44" t="s">
         <v>169</v>
       </c>
-      <c r="C44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" t="s">
-        <v>169</v>
-      </c>
-      <c r="F44" t="s">
-        <v>172</v>
-      </c>
-      <c r="G44" t="s">
-        <v>173</v>
-      </c>
       <c r="H44" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="I44" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J44" t="s">
         <v>9</v>
@@ -2178,7 +2167,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2186,28 +2175,28 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" t="s">
+        <v>174</v>
+      </c>
+      <c r="G46" t="s">
         <v>175</v>
       </c>
-      <c r="C46" t="s">
-        <v>175</v>
-      </c>
-      <c r="D46" t="s">
-        <v>177</v>
-      </c>
-      <c r="E46" t="s">
-        <v>175</v>
-      </c>
-      <c r="F46" t="s">
-        <v>178</v>
-      </c>
-      <c r="G46" t="s">
-        <v>179</v>
-      </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I46" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="J46" t="s">
         <v>9</v>
@@ -2215,7 +2204,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2223,28 +2212,28 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" t="s">
+        <v>179</v>
+      </c>
+      <c r="G48" t="s">
         <v>180</v>
       </c>
-      <c r="C48" t="s">
-        <v>180</v>
-      </c>
-      <c r="D48" t="s">
-        <v>182</v>
-      </c>
-      <c r="E48" t="s">
-        <v>180</v>
-      </c>
-      <c r="F48" t="s">
-        <v>183</v>
-      </c>
-      <c r="G48" t="s">
-        <v>184</v>
-      </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I48" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J48" t="s">
         <v>9</v>
@@ -2252,7 +2241,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2260,28 +2249,28 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="J50" t="s">
         <v>9</v>
@@ -2289,7 +2278,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2297,28 +2286,28 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s">
         <v>188</v>
-      </c>
-      <c r="C52" t="s">
-        <v>188</v>
-      </c>
-      <c r="D52" t="s">
-        <v>190</v>
-      </c>
-      <c r="E52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F52" t="s">
-        <v>191</v>
-      </c>
-      <c r="G52" t="s">
-        <v>192</v>
-      </c>
-      <c r="H52" t="s">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s">
-        <v>193</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2326,7 +2315,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2334,36 +2323,36 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G54" t="s">
+        <v>193</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
         <v>194</v>
       </c>
-      <c r="C54" t="s">
-        <v>194</v>
-      </c>
-      <c r="D54" t="s">
-        <v>196</v>
-      </c>
-      <c r="E54" t="s">
-        <v>194</v>
-      </c>
-      <c r="F54" t="s">
-        <v>197</v>
-      </c>
-      <c r="G54" t="s">
-        <v>198</v>
-      </c>
-      <c r="H54" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" t="s">
-        <v>199</v>
-      </c>
       <c r="J54" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2371,36 +2360,36 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E56" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F56" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G56" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I56" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J56" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>201</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2408,36 +2397,36 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" t="s">
+        <v>199</v>
+      </c>
+      <c r="E58" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" t="s">
+        <v>200</v>
+      </c>
+      <c r="G58" t="s">
         <v>56</v>
       </c>
-      <c r="C58" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" t="s">
-        <v>206</v>
-      </c>
-      <c r="E58" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" t="s">
-        <v>207</v>
-      </c>
-      <c r="G58" t="s">
-        <v>58</v>
-      </c>
       <c r="H58" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2445,36 +2434,36 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E60" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="F60" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G60" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="H60" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>213</v>
+        <v>30</v>
       </c>
       <c r="J60" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>209</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2482,36 +2471,36 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="D62" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="F62" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G62" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I62" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="J62" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -2519,36 +2508,36 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C64" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F64" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="G64" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H64" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I64" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="J64" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2556,36 +2545,36 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C66" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D66" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E66" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="G66" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="H66" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="I66" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="J66" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2593,36 +2582,36 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C68" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D68" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E68" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F68" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G68" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>221</v>
       </c>
       <c r="J68" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2630,36 +2619,36 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C70" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D70" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E70" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F70" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="G70" t="s">
-        <v>236</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="I70" t="s">
-        <v>237</v>
+        <v>84</v>
       </c>
       <c r="J70" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2667,36 +2656,36 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C72" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D72" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E72" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F72" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G72" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="J72" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2704,36 +2693,36 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C74" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D74" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E74" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="F74" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G74" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="H74" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="I74" t="s">
-        <v>248</v>
+        <v>76</v>
       </c>
       <c r="J74" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -2741,36 +2730,36 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="D76" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="E76" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="F76" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="G76" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="H76" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I76" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="J76" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>250</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -2778,36 +2767,36 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="D78" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="E78" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="F78" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="G78" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="H78" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="J78" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2815,36 +2804,36 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D80" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E80" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="F80" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G80" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="H80" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I80" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="J80" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2852,36 +2841,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C82" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D82" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E82" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F82" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G82" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="H82" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="J82" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -2889,36 +2878,36 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="C84" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="D84" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E84" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="F84" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="G84" t="s">
-        <v>53</v>
+        <v>260</v>
       </c>
       <c r="H84" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I84" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="J84" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>52</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -2926,36 +2915,36 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="C86" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="G86" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H86" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="I86" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="J86" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -2963,36 +2952,36 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="C88" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="D88" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="F88" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G88" t="s">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>65</v>
+        <v>272</v>
       </c>
       <c r="J88" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3000,36 +2989,36 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
+        <v>273</v>
+      </c>
+      <c r="C90" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" t="s">
+        <v>275</v>
+      </c>
+      <c r="E90" t="s">
+        <v>273</v>
+      </c>
+      <c r="F90" t="s">
         <v>276</v>
       </c>
-      <c r="C90" t="s">
-        <v>276</v>
-      </c>
-      <c r="D90" t="s">
-        <v>278</v>
-      </c>
-      <c r="E90" t="s">
-        <v>276</v>
-      </c>
-      <c r="F90" t="s">
-        <v>279</v>
-      </c>
       <c r="G90" t="s">
-        <v>280</v>
+        <v>106</v>
       </c>
       <c r="H90" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I90" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J90" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3037,36 +3026,36 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>278</v>
       </c>
       <c r="C92" t="s">
-        <v>68</v>
+        <v>278</v>
       </c>
       <c r="D92" t="s">
+        <v>280</v>
+      </c>
+      <c r="E92" t="s">
+        <v>278</v>
+      </c>
+      <c r="F92" t="s">
+        <v>281</v>
+      </c>
+      <c r="G92" t="s">
+        <v>114</v>
+      </c>
+      <c r="H92" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" t="s">
         <v>282</v>
       </c>
-      <c r="E92" t="s">
-        <v>68</v>
-      </c>
-      <c r="F92" t="s">
-        <v>283</v>
-      </c>
-      <c r="G92" t="s">
-        <v>70</v>
-      </c>
-      <c r="H92" t="s">
-        <v>8</v>
-      </c>
-      <c r="I92" t="s">
-        <v>64</v>
-      </c>
       <c r="J92" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>69</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3074,28 +3063,28 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D94" t="s">
+        <v>285</v>
+      </c>
+      <c r="E94" t="s">
+        <v>283</v>
+      </c>
+      <c r="F94" t="s">
         <v>286</v>
       </c>
-      <c r="E94" t="s">
-        <v>284</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>287</v>
       </c>
-      <c r="G94" t="s">
-        <v>288</v>
-      </c>
       <c r="H94" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="J94" t="s">
         <v>9</v>
@@ -3103,7 +3092,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3111,28 +3100,28 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
+        <v>288</v>
+      </c>
+      <c r="C96" t="s">
+        <v>288</v>
+      </c>
+      <c r="D96" t="s">
         <v>290</v>
       </c>
-      <c r="C96" t="s">
-        <v>290</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" t="s">
+        <v>291</v>
+      </c>
+      <c r="G96" t="s">
         <v>292</v>
       </c>
-      <c r="E96" t="s">
-        <v>290</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="H96" t="s">
+        <v>26</v>
+      </c>
+      <c r="I96" t="s">
         <v>293</v>
-      </c>
-      <c r="G96" t="s">
-        <v>294</v>
-      </c>
-      <c r="H96" t="s">
-        <v>18</v>
-      </c>
-      <c r="I96" t="s">
-        <v>295</v>
       </c>
       <c r="J96" t="s">
         <v>9</v>
@@ -3140,7 +3129,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3148,36 +3137,36 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
+        <v>294</v>
+      </c>
+      <c r="C98" t="s">
+        <v>294</v>
+      </c>
+      <c r="D98" t="s">
         <v>296</v>
       </c>
-      <c r="C98" t="s">
-        <v>296</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>294</v>
+      </c>
+      <c r="F98" t="s">
+        <v>297</v>
+      </c>
+      <c r="G98" t="s">
         <v>298</v>
       </c>
-      <c r="E98" t="s">
-        <v>296</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" t="s">
         <v>299</v>
       </c>
-      <c r="G98" t="s">
-        <v>133</v>
-      </c>
-      <c r="H98" t="s">
-        <v>18</v>
-      </c>
-      <c r="I98" t="s">
-        <v>300</v>
-      </c>
       <c r="J98" t="s">
-        <v>231</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3185,36 +3174,36 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
+        <v>87</v>
+      </c>
+      <c r="C100" t="s">
+        <v>87</v>
+      </c>
+      <c r="D100" t="s">
+        <v>300</v>
+      </c>
+      <c r="E100" t="s">
+        <v>87</v>
+      </c>
+      <c r="F100" t="s">
         <v>301</v>
       </c>
-      <c r="C100" t="s">
-        <v>301</v>
-      </c>
-      <c r="D100" t="s">
-        <v>303</v>
-      </c>
-      <c r="E100" t="s">
-        <v>301</v>
-      </c>
-      <c r="F100" t="s">
-        <v>304</v>
-      </c>
       <c r="G100" t="s">
-        <v>305</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I100" t="s">
-        <v>306</v>
+        <v>90</v>
       </c>
       <c r="J100" t="s">
-        <v>231</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>302</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{273AE238-3077-4F10-A66D-9A234204C7FE}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82938C83-5300-4F05-B270-D5B51518CD7B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CD7A04BB-561F-44B5-BA10-41E0FF983FF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="320">
   <si>
     <t>Symbol</t>
   </si>
@@ -68,27 +68,9 @@
     <t>Robust</t>
   </si>
   <si>
-    <t>Virtus Investment Partners, Inc.</t>
-  </si>
-  <si>
-    <t>VRTS</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
     <t>6.0</t>
   </si>
   <si>
-    <t>-2.71</t>
-  </si>
-  <si>
-    <t>Northpointe Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>NPB</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -137,27 +119,12 @@
     <t>4.0</t>
   </si>
   <si>
-    <t>First Internet Bancorp</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
     <t>NB Bancorp, Inc. Common Stock</t>
   </si>
   <si>
     <t>NBBK</t>
   </si>
   <si>
-    <t>Univest Financial Corporation</t>
-  </si>
-  <si>
-    <t>UVSP</t>
-  </si>
-  <si>
     <t>American Integrity Insurance Group, Inc.</t>
   </si>
   <si>
@@ -185,9 +152,6 @@
     <t>1.38</t>
   </si>
   <si>
-    <t>-3.79</t>
-  </si>
-  <si>
     <t>Meridian Corporation</t>
   </si>
   <si>
@@ -206,15 +170,6 @@
     <t>TSBK</t>
   </si>
   <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>-3.56</t>
-  </si>
-  <si>
     <t>Parke Bancorp, Inc.</t>
   </si>
   <si>
@@ -233,18 +188,6 @@
     <t>-3.47</t>
   </si>
   <si>
-    <t>Home Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>HBCP</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>-3.59</t>
-  </si>
-  <si>
     <t>Silvercrest Asset Management Group Inc.</t>
   </si>
   <si>
@@ -266,21 +209,6 @@
     <t>0.25</t>
   </si>
   <si>
-    <t>-3.64</t>
-  </si>
-  <si>
-    <t>First Business Financial Services, Inc.</t>
-  </si>
-  <si>
-    <t>FBIZ</t>
-  </si>
-  <si>
-    <t>1.28</t>
-  </si>
-  <si>
-    <t>-3.17</t>
-  </si>
-  <si>
     <t>FactSet Research Systems Inc.</t>
   </si>
   <si>
@@ -293,12 +221,6 @@
     <t>-2.50</t>
   </si>
   <si>
-    <t>South Plains Financial, Inc.</t>
-  </si>
-  <si>
-    <t>SPFI</t>
-  </si>
-  <si>
     <t>Amerant Bancorp Inc.</t>
   </si>
   <si>
@@ -311,637 +233,769 @@
     <t>-5.53</t>
   </si>
   <si>
-    <t>Citizens Community Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>CZWI</t>
-  </si>
-  <si>
-    <t>United Cooperative Assurance Company</t>
-  </si>
-  <si>
-    <t>8190.SR</t>
-  </si>
-  <si>
-    <t>Al Alamiya for Cooperative Insurance Company</t>
-  </si>
-  <si>
-    <t>8280.SR</t>
-  </si>
-  <si>
     <t>Resilient</t>
   </si>
   <si>
-    <t>Amlak International for Real Estate Finance Company</t>
-  </si>
-  <si>
-    <t>1182.SR</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>-3.50</t>
-  </si>
-  <si>
-    <t>Sound Financial Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>SFBC</t>
-  </si>
-  <si>
-    <t>Community West Bancshares</t>
-  </si>
-  <si>
-    <t>CWBC</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Midland States Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>MSBI</t>
-  </si>
-  <si>
-    <t>-3.34</t>
-  </si>
-  <si>
-    <t>Independent Bank Corporation</t>
-  </si>
-  <si>
-    <t>IBCP</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
     <t>-4.25</t>
   </si>
   <si>
     <t>0.18</t>
   </si>
   <si>
-    <t>Landmark Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>LARK</t>
-  </si>
-  <si>
     <t>PRA Group, Inc.</t>
   </si>
   <si>
     <t>PRAA</t>
   </si>
   <si>
-    <t>866.51M</t>
-  </si>
-  <si>
-    <t>+234.27</t>
-  </si>
-  <si>
-    <t>8.65B</t>
-  </si>
-  <si>
-    <t>+74.50</t>
-  </si>
-  <si>
-    <t>960.50M</t>
-  </si>
-  <si>
-    <t>+65.45</t>
-  </si>
-  <si>
-    <t>266.98M</t>
-  </si>
-  <si>
-    <t>+54.62</t>
-  </si>
-  <si>
-    <t>339.36M</t>
-  </si>
-  <si>
-    <t>+40.73</t>
-  </si>
-  <si>
-    <t>311.08M</t>
-  </si>
-  <si>
-    <t>+29.49</t>
-  </si>
-  <si>
     <t>0.41</t>
   </si>
   <si>
-    <t>410.43M</t>
-  </si>
-  <si>
-    <t>+27.40</t>
-  </si>
-  <si>
-    <t>801.57M</t>
-  </si>
-  <si>
-    <t>+51.96</t>
-  </si>
-  <si>
     <t>Southside Bancshares, Inc.</t>
   </si>
   <si>
     <t>SBSI</t>
   </si>
   <si>
-    <t>998.44M</t>
-  </si>
-  <si>
-    <t>+32.69</t>
-  </si>
-  <si>
     <t>0.14</t>
   </si>
   <si>
     <t>-3.24</t>
   </si>
   <si>
-    <t>1.04B</t>
-  </si>
-  <si>
-    <t>+29.80</t>
-  </si>
-  <si>
-    <t>221.63M</t>
-  </si>
-  <si>
-    <t>+25.45</t>
-  </si>
-  <si>
-    <t>351.61M</t>
-  </si>
-  <si>
-    <t>+25.29</t>
-  </si>
-  <si>
-    <t>322.91M</t>
-  </si>
-  <si>
-    <t>+15.24</t>
-  </si>
-  <si>
-    <t>174.46M</t>
-  </si>
-  <si>
-    <t>+12.87</t>
-  </si>
-  <si>
-    <t>479.93M</t>
-  </si>
-  <si>
-    <t>+12.44</t>
-  </si>
-  <si>
-    <t>114.87M</t>
-  </si>
-  <si>
-    <t>+10.90</t>
-  </si>
-  <si>
-    <t>553.62M</t>
-  </si>
-  <si>
-    <t>+9.54</t>
-  </si>
-  <si>
-    <t>465.92M</t>
-  </si>
-  <si>
-    <t>+5.10</t>
-  </si>
-  <si>
-    <t>679.58M</t>
-  </si>
-  <si>
-    <t>+4.24</t>
-  </si>
-  <si>
-    <t>152.53M</t>
-  </si>
-  <si>
-    <t>-0.25</t>
-  </si>
-  <si>
-    <t>670.61M</t>
-  </si>
-  <si>
     <t>-1.47</t>
   </si>
   <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>198.99M</t>
-  </si>
-  <si>
-    <t>-2.15</t>
-  </si>
-  <si>
-    <t>1.19</t>
-  </si>
-  <si>
-    <t>-2.73</t>
-  </si>
-  <si>
-    <t>Red River Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>RRBI</t>
-  </si>
-  <si>
-    <t>590.94M</t>
-  </si>
-  <si>
-    <t>-7.45</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Ames National Corporation</t>
-  </si>
-  <si>
-    <t>ATLO</t>
-  </si>
-  <si>
-    <t>251.19M</t>
-  </si>
-  <si>
-    <t>-16.91</t>
-  </si>
-  <si>
-    <t>1.31</t>
-  </si>
-  <si>
-    <t>-2.61</t>
-  </si>
-  <si>
-    <t>31.78M</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>-3.15</t>
-  </si>
-  <si>
-    <t>202.70M</t>
-  </si>
-  <si>
-    <t>-65.37</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
     <t>-2.75</t>
   </si>
   <si>
-    <t>Donegal Group Inc.</t>
-  </si>
-  <si>
-    <t>DGICA</t>
-  </si>
-  <si>
-    <t>521.08M</t>
-  </si>
-  <si>
-    <t>+159.29</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>-3.67</t>
-  </si>
-  <si>
-    <t>104.89M</t>
-  </si>
-  <si>
-    <t>+102.75</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>11.54</t>
-  </si>
-  <si>
-    <t>108.47M</t>
-  </si>
-  <si>
-    <t>+89.28</t>
-  </si>
-  <si>
-    <t>451.72M</t>
-  </si>
-  <si>
-    <t>+56.16</t>
-  </si>
-  <si>
-    <t>159.38M</t>
-  </si>
-  <si>
-    <t>+23.24</t>
-  </si>
-  <si>
-    <t>Westwood Holdings Group, Inc.</t>
-  </si>
-  <si>
-    <t>WHG</t>
-  </si>
-  <si>
-    <t>142.26M</t>
-  </si>
-  <si>
-    <t>+23.00</t>
-  </si>
-  <si>
-    <t>4.70</t>
-  </si>
-  <si>
-    <t>-2.69</t>
-  </si>
-  <si>
-    <t>Saudi Arabian Cooperative Insurance Company</t>
-  </si>
-  <si>
-    <t>8100.SR</t>
-  </si>
-  <si>
-    <t>69.35M</t>
-  </si>
-  <si>
-    <t>+20.18</t>
-  </si>
-  <si>
-    <t>1.76</t>
-  </si>
-  <si>
-    <t>Chubb Arabia Cooperative Insurance Company</t>
-  </si>
-  <si>
-    <t>8240.SR</t>
-  </si>
-  <si>
-    <t>194.18M</t>
-  </si>
-  <si>
-    <t>+51.30</t>
-  </si>
-  <si>
-    <t>2.99</t>
-  </si>
-  <si>
-    <t>-2.46</t>
-  </si>
-  <si>
-    <t>LCNB Corp.</t>
-  </si>
-  <si>
-    <t>LCNB</t>
-  </si>
-  <si>
-    <t>226.64M</t>
-  </si>
-  <si>
-    <t>+40.11</t>
-  </si>
-  <si>
-    <t>Fidelity D &amp; D Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>FDBC</t>
-  </si>
-  <si>
-    <t>260.74M</t>
-  </si>
-  <si>
-    <t>+19.17</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>-4.41</t>
-  </si>
-  <si>
-    <t>Western New England Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>WNEB</t>
-  </si>
-  <si>
-    <t>277.35M</t>
-  </si>
-  <si>
-    <t>+2.81</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>286.70M</t>
-  </si>
-  <si>
-    <t>+73.65</t>
-  </si>
-  <si>
-    <t>First United Corporation</t>
-  </si>
-  <si>
-    <t>FUNC</t>
-  </si>
-  <si>
-    <t>240.32M</t>
-  </si>
-  <si>
-    <t>-13.42</t>
-  </si>
-  <si>
-    <t>-4.75</t>
-  </si>
-  <si>
-    <t>Southern California Bancorp</t>
-  </si>
-  <si>
-    <t>BCAL</t>
-  </si>
-  <si>
-    <t>607.77M</t>
-  </si>
-  <si>
-    <t>+91.83</t>
-  </si>
-  <si>
     <t>0.36</t>
   </si>
   <si>
-    <t>-3.46</t>
-  </si>
-  <si>
-    <t>Hawthorn Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>HWBK</t>
-  </si>
-  <si>
-    <t>232.79M</t>
-  </si>
-  <si>
-    <t>+242.53</t>
-  </si>
-  <si>
-    <t>-3.44</t>
-  </si>
-  <si>
     <t>Steady</t>
   </si>
   <si>
-    <t>LINKBANCORP, Inc.</t>
-  </si>
-  <si>
-    <t>LNKB</t>
-  </si>
-  <si>
-    <t>323.85M</t>
-  </si>
-  <si>
-    <t>+63.98</t>
-  </si>
-  <si>
-    <t>-0.70</t>
-  </si>
-  <si>
-    <t>-3.28</t>
-  </si>
-  <si>
-    <t>NZX Limited</t>
-  </si>
-  <si>
-    <t>NZX.NZ</t>
-  </si>
-  <si>
-    <t>271.02M</t>
-  </si>
-  <si>
     <t>+37.14</t>
   </si>
   <si>
-    <t>3.04</t>
-  </si>
-  <si>
-    <t>LendingTree, Inc.</t>
-  </si>
-  <si>
-    <t>TREE</t>
-  </si>
-  <si>
-    <t>565.13M</t>
-  </si>
-  <si>
-    <t>+35.52</t>
-  </si>
-  <si>
-    <t>1.43</t>
-  </si>
-  <si>
-    <t>-2.59</t>
-  </si>
-  <si>
-    <t>C&amp;F Financial Corporation</t>
-  </si>
-  <si>
-    <t>CFFI</t>
-  </si>
-  <si>
-    <t>249.06M</t>
-  </si>
-  <si>
-    <t>+34.80</t>
-  </si>
-  <si>
-    <t>-3.19</t>
-  </si>
-  <si>
-    <t>USCB Financial Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>USCB</t>
-  </si>
-  <si>
-    <t>333.52M</t>
-  </si>
-  <si>
-    <t>+33.81</t>
-  </si>
-  <si>
     <t>-4.34</t>
   </si>
   <si>
-    <t>Employers Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>EIG</t>
-  </si>
-  <si>
-    <t>1.02B</t>
-  </si>
-  <si>
-    <t>+22.50</t>
-  </si>
-  <si>
-    <t>1.81</t>
-  </si>
-  <si>
-    <t>Heritage Financial Corporation</t>
-  </si>
-  <si>
-    <t>HFWA</t>
-  </si>
-  <si>
-    <t>1.06B</t>
-  </si>
-  <si>
-    <t>+8.71</t>
-  </si>
-  <si>
     <t>1.18</t>
   </si>
   <si>
-    <t>-2.42</t>
-  </si>
-  <si>
     <t>Hanmi Financial Corporation</t>
   </si>
   <si>
     <t>HAFC</t>
   </si>
   <si>
-    <t>892.13M</t>
-  </si>
-  <si>
-    <t>+5.85</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>7.22</t>
-  </si>
-  <si>
-    <t>920.81M</t>
-  </si>
-  <si>
-    <t>+4.16</t>
+    <t>BNP Paribas S.A.</t>
+  </si>
+  <si>
+    <t>BNP.PA</t>
+  </si>
+  <si>
+    <t>116.29B</t>
+  </si>
+  <si>
+    <t>+50.83</t>
+  </si>
+  <si>
+    <t>-0.14</t>
+  </si>
+  <si>
+    <t>-2.18</t>
+  </si>
+  <si>
+    <t>AXA S.A.</t>
+  </si>
+  <si>
+    <t>CS.PA</t>
+  </si>
+  <si>
+    <t>98.55B</t>
+  </si>
+  <si>
+    <t>+55.15</t>
+  </si>
+  <si>
+    <t>-1.37</t>
+  </si>
+  <si>
+    <t>845.35M</t>
+  </si>
+  <si>
+    <t>+242.63</t>
+  </si>
+  <si>
+    <t>332.12M</t>
+  </si>
+  <si>
+    <t>+43.80</t>
+  </si>
+  <si>
+    <t>826.36M</t>
+  </si>
+  <si>
+    <t>+47.40</t>
+  </si>
+  <si>
+    <t>SB Financial Group, Inc.</t>
+  </si>
+  <si>
+    <t>SBFG</t>
+  </si>
+  <si>
+    <t>134.79M</t>
+  </si>
+  <si>
+    <t>+33.90</t>
+  </si>
+  <si>
+    <t>-2.56</t>
+  </si>
+  <si>
+    <t>FS Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>FSBW</t>
+  </si>
+  <si>
+    <t>302.22M</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>-2.30</t>
+  </si>
+  <si>
+    <t>209.29M</t>
+  </si>
+  <si>
+    <t>+32.84</t>
+  </si>
+  <si>
+    <t>Quálitas Controladora, S.A.B. de C.V.</t>
+  </si>
+  <si>
+    <t>Q.MX</t>
+  </si>
+  <si>
+    <t>3.95B</t>
+  </si>
+  <si>
+    <t>+30.71</t>
+  </si>
+  <si>
+    <t>1.56</t>
+  </si>
+  <si>
+    <t>-7.14</t>
+  </si>
+  <si>
+    <t>404.39M</t>
+  </si>
+  <si>
+    <t>+29.31</t>
+  </si>
+  <si>
+    <t>321.24M</t>
+  </si>
+  <si>
+    <t>+25.40</t>
+  </si>
+  <si>
+    <t>Peoples Bancorp of North Carolina, Inc.</t>
+  </si>
+  <si>
+    <t>PEBK</t>
+  </si>
+  <si>
+    <t>211.91M</t>
+  </si>
+  <si>
+    <t>+23.33</t>
+  </si>
+  <si>
+    <t>-3.61</t>
+  </si>
+  <si>
+    <t>359.08M</t>
+  </si>
+  <si>
+    <t>+22.68</t>
+  </si>
+  <si>
+    <t>Globe Life Inc.</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>12.03B</t>
+  </si>
+  <si>
+    <t>+21.10</t>
+  </si>
+  <si>
+    <t>1.68</t>
+  </si>
+  <si>
+    <t>175.54M</t>
+  </si>
+  <si>
+    <t>+15.03</t>
+  </si>
+  <si>
+    <t>-0.69</t>
+  </si>
+  <si>
+    <t>326.95M</t>
+  </si>
+  <si>
+    <t>+13.81</t>
+  </si>
+  <si>
+    <t>893.91M</t>
+  </si>
+  <si>
+    <t>+13.79</t>
+  </si>
+  <si>
+    <t>-4.64</t>
+  </si>
+  <si>
+    <t>Amalgamated Financial Corp.</t>
+  </si>
+  <si>
+    <t>AMAL</t>
+  </si>
+  <si>
+    <t>1.23B</t>
+  </si>
+  <si>
+    <t>+14.97</t>
+  </si>
+  <si>
+    <t>-2.47</t>
+  </si>
+  <si>
+    <t>TrustCo Bank Corp NY</t>
+  </si>
+  <si>
+    <t>TRST</t>
+  </si>
+  <si>
+    <t>859.48M</t>
+  </si>
+  <si>
+    <t>+11.83</t>
+  </si>
+  <si>
+    <t>-3.45</t>
+  </si>
+  <si>
+    <t>115.97M</t>
+  </si>
+  <si>
+    <t>+9.85</t>
+  </si>
+  <si>
+    <t>929.28M</t>
+  </si>
+  <si>
+    <t>+3.21</t>
+  </si>
+  <si>
+    <t>1.00B</t>
+  </si>
+  <si>
+    <t>+31.97</t>
+  </si>
+  <si>
+    <t>148.03M</t>
+  </si>
+  <si>
+    <t>+2.78</t>
+  </si>
+  <si>
+    <t>SLM Corporation</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>4.42B</t>
+  </si>
+  <si>
+    <t>+0.77</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>-5.13</t>
+  </si>
+  <si>
+    <t>Dai-ichi Life Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>8750.T</t>
+  </si>
+  <si>
+    <t>32.75B</t>
+  </si>
+  <si>
+    <t>+114.26</t>
+  </si>
+  <si>
+    <t>-3.35</t>
+  </si>
+  <si>
+    <t>PayPal Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>PYPL</t>
+  </si>
+  <si>
+    <t>42.07B</t>
+  </si>
+  <si>
+    <t>+88.59</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>52.96</t>
+  </si>
+  <si>
+    <t>The Company for Cooperative Insurance</t>
+  </si>
+  <si>
+    <t>8010.SR</t>
+  </si>
+  <si>
+    <t>5.14B</t>
+  </si>
+  <si>
+    <t>+37.65</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>-3.16</t>
+  </si>
+  <si>
+    <t>Federated Hermes, Inc.</t>
+  </si>
+  <si>
+    <t>FHI</t>
+  </si>
+  <si>
+    <t>4.04B</t>
+  </si>
+  <si>
+    <t>+20.32</t>
+  </si>
+  <si>
+    <t>6.07</t>
+  </si>
+  <si>
+    <t>-3.21</t>
+  </si>
+  <si>
+    <t>Principal Financial Group, Inc.</t>
+  </si>
+  <si>
+    <t>PFG</t>
+  </si>
+  <si>
+    <t>22.07B</t>
+  </si>
+  <si>
+    <t>+13.99</t>
+  </si>
+  <si>
+    <t>Scottish Mortgage Investment Trust PLC</t>
+  </si>
+  <si>
+    <t>SMT.L</t>
+  </si>
+  <si>
+    <t>22.58B</t>
+  </si>
+  <si>
+    <t>+39.77</t>
+  </si>
+  <si>
+    <t>5.92</t>
+  </si>
+  <si>
+    <t>-1.13</t>
+  </si>
+  <si>
+    <t>MSCI Inc.</t>
+  </si>
+  <si>
+    <t>MSCI</t>
+  </si>
+  <si>
+    <t>41.88B</t>
+  </si>
+  <si>
+    <t>+33.40</t>
+  </si>
+  <si>
+    <t>5.89</t>
+  </si>
+  <si>
+    <t>-3.11</t>
+  </si>
+  <si>
+    <t>Public Bank Berhad</t>
+  </si>
+  <si>
+    <t>1295.KL</t>
+  </si>
+  <si>
+    <t>23.17B</t>
+  </si>
+  <si>
+    <t>+30.11</t>
+  </si>
+  <si>
+    <t>-0.02</t>
+  </si>
+  <si>
+    <t>-4.42</t>
+  </si>
+  <si>
+    <t>MS&amp;AD Insurance Group Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>8725.T</t>
+  </si>
+  <si>
+    <t>37.43B</t>
+  </si>
+  <si>
+    <t>+28.63</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>The Allstate Corporation</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>56.73B</t>
+  </si>
+  <si>
+    <t>+37.79</t>
+  </si>
+  <si>
+    <t>1.34</t>
+  </si>
+  <si>
+    <t>-3.04</t>
+  </si>
+  <si>
+    <t>London Stock Exchange Group plc</t>
+  </si>
+  <si>
+    <t>LSEG.L</t>
+  </si>
+  <si>
+    <t>68.24B</t>
+  </si>
+  <si>
+    <t>+37.09</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>-3.31</t>
+  </si>
+  <si>
+    <t>Victory Capital Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>VCTR</t>
+  </si>
+  <si>
+    <t>5.26B</t>
+  </si>
+  <si>
+    <t>-0.55</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>-554.81</t>
+  </si>
+  <si>
+    <t>Hong Leong Financial Group Berhad</t>
+  </si>
+  <si>
+    <t>1082.KL</t>
+  </si>
+  <si>
+    <t>5.44B</t>
+  </si>
+  <si>
+    <t>+62.37</t>
+  </si>
+  <si>
+    <t>-0.53</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>-4.02</t>
+  </si>
+  <si>
+    <t>The Hartford Financial Services Group, Inc.</t>
+  </si>
+  <si>
+    <t>HIG</t>
+  </si>
+  <si>
+    <t>37.93B</t>
+  </si>
+  <si>
+    <t>-3.37</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>Selective Insurance Group, Inc.</t>
+  </si>
+  <si>
+    <t>SIGI</t>
+  </si>
+  <si>
+    <t>4.97B</t>
+  </si>
+  <si>
+    <t>+55.99</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>-12.72</t>
+  </si>
+  <si>
+    <t>Nelnet, Inc.</t>
+  </si>
+  <si>
+    <t>NNI</t>
+  </si>
+  <si>
+    <t>5.10B</t>
+  </si>
+  <si>
+    <t>+51.51</t>
+  </si>
+  <si>
+    <t>-2.87</t>
+  </si>
+  <si>
+    <t>Bank OZK</t>
+  </si>
+  <si>
+    <t>OZK</t>
+  </si>
+  <si>
+    <t>5.36B</t>
+  </si>
+  <si>
+    <t>+33.08</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>-3.68</t>
+  </si>
+  <si>
+    <t>Arch Capital Group Ltd.</t>
+  </si>
+  <si>
+    <t>ACGL</t>
+  </si>
+  <si>
+    <t>34.80B</t>
+  </si>
+  <si>
+    <t>-4.11</t>
+  </si>
+  <si>
+    <t>-4.63</t>
+  </si>
+  <si>
+    <t>Axos Financial, Inc.</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>4.94B</t>
+  </si>
+  <si>
+    <t>-9.85</t>
+  </si>
+  <si>
+    <t>-5.88</t>
+  </si>
+  <si>
+    <t>Morningstar, Inc.</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>6.39B</t>
+  </si>
+  <si>
+    <t>+145.86</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>-2.51</t>
+  </si>
+  <si>
+    <t>7.72B</t>
+  </si>
+  <si>
+    <t>+94.20</t>
+  </si>
+  <si>
+    <t>United Overseas Bank Limited</t>
+  </si>
+  <si>
+    <t>U11.SI</t>
+  </si>
+  <si>
+    <t>48.26B</t>
+  </si>
+  <si>
+    <t>+73.54</t>
+  </si>
+  <si>
+    <t>-0.57</t>
+  </si>
+  <si>
+    <t>-1.95</t>
+  </si>
+  <si>
+    <t>First American Financial Corporation</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>7.06B</t>
+  </si>
+  <si>
+    <t>+62.34</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>DNB Bank ASA</t>
+  </si>
+  <si>
+    <t>DNB.OL</t>
+  </si>
+  <si>
+    <t>43.74B</t>
+  </si>
+  <si>
+    <t>+53.79</t>
+  </si>
+  <si>
+    <t>-0.36</t>
+  </si>
+  <si>
+    <t>-3.70</t>
+  </si>
+  <si>
+    <t>Willis Towers Watson Public Limited Company</t>
+  </si>
+  <si>
+    <t>WTW</t>
+  </si>
+  <si>
+    <t>24.67B</t>
+  </si>
+  <si>
+    <t>+38.70</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>-2.49</t>
+  </si>
+  <si>
+    <t>St. James's Place plc</t>
+  </si>
+  <si>
+    <t>STJ.L</t>
+  </si>
+  <si>
+    <t>8.62B</t>
+  </si>
+  <si>
+    <t>+35.36</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>United Community Banks, Inc.</t>
+  </si>
+  <si>
+    <t>UCB</t>
+  </si>
+  <si>
+    <t>+34.94</t>
+  </si>
+  <si>
+    <t>-3.57</t>
+  </si>
+  <si>
+    <t>Marsh &amp; McLennan Companies, Inc.</t>
+  </si>
+  <si>
+    <t>MRSH</t>
+  </si>
+  <si>
+    <t>80.32B</t>
+  </si>
+  <si>
+    <t>+31.04</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>-2.14</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815B5833-788F-4279-8BDF-C70713B76FD4}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1358,105 +1412,105 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
         <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>9</v>
@@ -1464,36 +1518,36 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
         <v>9</v>
@@ -1501,36 +1555,36 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
@@ -1538,36 +1592,36 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="J12" t="s">
         <v>9</v>
@@ -1575,36 +1629,36 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="J14" t="s">
         <v>9</v>
@@ -1612,36 +1666,36 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" t="s">
-        <v>135</v>
-      </c>
-      <c r="G16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" t="s">
-        <v>25</v>
-      </c>
       <c r="I16" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J16" t="s">
         <v>9</v>
@@ -1649,36 +1703,36 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
         <v>9</v>
@@ -1686,36 +1740,36 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
         <v>10</v>
       </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
       <c r="I20" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s">
         <v>9</v>
@@ -1723,36 +1777,36 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I22" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J22" t="s">
         <v>9</v>
@@ -1760,36 +1814,36 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="J24" t="s">
         <v>9</v>
@@ -1797,36 +1851,36 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -1834,36 +1888,36 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s">
         <v>9</v>
@@ -1871,36 +1925,36 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J30" t="s">
         <v>9</v>
@@ -1908,36 +1962,36 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
         <v>9</v>
@@ -1945,36 +1999,36 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="J34" t="s">
         <v>9</v>
@@ -1982,36 +2036,36 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="J36" t="s">
         <v>9</v>
@@ -2019,36 +2073,36 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="F38" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G38" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
@@ -2056,36 +2110,36 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G40" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
         <v>9</v>
@@ -2093,36 +2147,36 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G42" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -2130,36 +2184,36 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G44" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="J44" t="s">
         <v>9</v>
@@ -2167,36 +2221,36 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>33</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J46" t="s">
         <v>9</v>
@@ -2204,36 +2258,36 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E48" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="F48" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G48" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I48" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J48" t="s">
         <v>9</v>
@@ -2241,36 +2295,36 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="G50" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J50" t="s">
         <v>9</v>
@@ -2278,36 +2332,36 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G52" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="I52" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2315,776 +2369,776 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D54" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F54" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G54" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I54" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="J54" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="F56" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G56" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I56" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="J56" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="J58" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="D60" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G60" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="J60" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="D62" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" t="s">
+        <v>200</v>
+      </c>
+      <c r="F62" t="s">
         <v>203</v>
       </c>
-      <c r="E62" t="s">
-        <v>115</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>204</v>
       </c>
-      <c r="G62" t="s">
-        <v>166</v>
-      </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I62" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J62" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J64" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="J66" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J68" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D70" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="H70" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="J70" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C72" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D72" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E72" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F72" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G72" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H72" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J72" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D74" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F74" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G74" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H74" t="s">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="I74" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="J74" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G76" t="s">
-        <v>100</v>
+        <v>246</v>
       </c>
       <c r="H76" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>99</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C78" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E78" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F78" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G78" t="s">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="H78" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J78" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C80" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D80" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E80" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F80" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="G80" t="s">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I80" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J80" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C82" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D82" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E82" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="G82" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="H82" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="J82" t="s">
-        <v>255</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C84" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D84" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E84" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G84" t="s">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J84" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F86" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G86" t="s">
-        <v>266</v>
+        <v>67</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="J86" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D88" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E88" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F88" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G88" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="J88" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
       <c r="C90" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
       <c r="D90" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E90" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
       <c r="F90" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G90" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>60</v>
       </c>
       <c r="J90" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>274</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C92" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E92" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F92" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G92" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I92" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J92" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E94" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F94" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G94" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I94" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="J94" t="s">
         <v>9</v>
@@ -3092,36 +3146,36 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D96" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F96" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G96" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H96" t="s">
         <v>26</v>
       </c>
       <c r="I96" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J96" t="s">
         <v>9</v>
@@ -3129,36 +3183,36 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B98" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C98" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D98" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E98" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F98" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G98" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H98" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I98" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
@@ -3166,36 +3220,36 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B100" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="C100" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="D100" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E100" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="F100" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G100" t="s">
-        <v>89</v>
+        <v>309</v>
       </c>
       <c r="H100" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I100" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J100" t="s">
         <v>9</v>
@@ -3203,7 +3257,81 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>88</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>49</v>
+      </c>
+      <c r="B102" t="s">
+        <v>310</v>
+      </c>
+      <c r="C102" t="s">
+        <v>310</v>
+      </c>
+      <c r="D102" t="s">
+        <v>186</v>
+      </c>
+      <c r="E102" t="s">
+        <v>310</v>
+      </c>
+      <c r="F102" t="s">
+        <v>312</v>
+      </c>
+      <c r="G102" t="s">
+        <v>56</v>
+      </c>
+      <c r="H102" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" t="s">
+        <v>313</v>
+      </c>
+      <c r="J102" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>50</v>
+      </c>
+      <c r="B104" t="s">
+        <v>314</v>
+      </c>
+      <c r="C104" t="s">
+        <v>314</v>
+      </c>
+      <c r="D104" t="s">
+        <v>316</v>
+      </c>
+      <c r="E104" t="s">
+        <v>314</v>
+      </c>
+      <c r="F104" t="s">
+        <v>317</v>
+      </c>
+      <c r="G104" t="s">
+        <v>318</v>
+      </c>
+      <c r="H104" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" t="s">
+        <v>319</v>
+      </c>
+      <c r="J104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4303082A-671C-4A87-8B8C-887764922B6B}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DAFEE75-A5EC-4253-BE25-917B951D994E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CD7A04BB-561F-44B5-BA10-41E0FF983FF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="313">
   <si>
     <t>Symbol</t>
   </si>
@@ -68,12 +68,6 @@
     <t>BNP.PA</t>
   </si>
   <si>
-    <t>116.15B</t>
-  </si>
-  <si>
-    <t>+50.04</t>
-  </si>
-  <si>
     <t>-0.14</t>
   </si>
   <si>
@@ -92,12 +86,6 @@
     <t>CS.PA</t>
   </si>
   <si>
-    <t>95.21B</t>
-  </si>
-  <si>
-    <t>+59.55</t>
-  </si>
-  <si>
     <t>0.36</t>
   </si>
   <si>
@@ -107,27 +95,9 @@
     <t>-1.37</t>
   </si>
   <si>
-    <t>PayPal Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>40.55B</t>
-  </si>
-  <si>
-    <t>+95.68</t>
-  </si>
-  <si>
-    <t>1.84</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>52.96</t>
-  </si>
-  <si>
     <t>Robust</t>
   </si>
   <si>
@@ -137,12 +107,6 @@
     <t>8250.SR</t>
   </si>
   <si>
-    <t>395.89M</t>
-  </si>
-  <si>
-    <t>+69.94</t>
-  </si>
-  <si>
     <t>1.46</t>
   </si>
   <si>
@@ -155,12 +119,6 @@
     <t>Q.MX</t>
   </si>
   <si>
-    <t>3.75B</t>
-  </si>
-  <si>
-    <t>+37.94</t>
-  </si>
-  <si>
     <t>1.56</t>
   </si>
   <si>
@@ -176,12 +134,6 @@
     <t>SBFG</t>
   </si>
   <si>
-    <t>132.45M</t>
-  </si>
-  <si>
-    <t>+36.27</t>
-  </si>
-  <si>
     <t>9.0</t>
   </si>
   <si>
@@ -194,12 +146,6 @@
     <t>FSBW</t>
   </si>
   <si>
-    <t>297.71M</t>
-  </si>
-  <si>
-    <t>+39.22</t>
-  </si>
-  <si>
     <t>0.31</t>
   </si>
   <si>
@@ -212,12 +158,6 @@
     <t>MRBK</t>
   </si>
   <si>
-    <t>202.56M</t>
-  </si>
-  <si>
-    <t>+37.26</t>
-  </si>
-  <si>
     <t>0.26</t>
   </si>
   <si>
@@ -230,12 +170,6 @@
     <t>TSBK</t>
   </si>
   <si>
-    <t>308.40M</t>
-  </si>
-  <si>
-    <t>+30.62</t>
-  </si>
-  <si>
     <t>0.41</t>
   </si>
   <si>
@@ -248,12 +182,6 @@
     <t>UVSP</t>
   </si>
   <si>
-    <t>1.05B</t>
-  </si>
-  <si>
-    <t>+26.60</t>
-  </si>
-  <si>
     <t>-0.68</t>
   </si>
   <si>
@@ -266,12 +194,6 @@
     <t>BCML</t>
   </si>
   <si>
-    <t>325.64M</t>
-  </si>
-  <si>
-    <t>+25.53</t>
-  </si>
-  <si>
     <t>0.29</t>
   </si>
   <si>
@@ -284,12 +206,6 @@
     <t>AII</t>
   </si>
   <si>
-    <t>334.21M</t>
-  </si>
-  <si>
-    <t>+38.31</t>
-  </si>
-  <si>
     <t>1.13</t>
   </si>
   <si>
@@ -302,9 +218,6 @@
     <t>PKBK</t>
   </si>
   <si>
-    <t>352.37M</t>
-  </si>
-  <si>
     <t>+25.02</t>
   </si>
   <si>
@@ -320,12 +233,6 @@
     <t>GCBC</t>
   </si>
   <si>
-    <t>422.27M</t>
-  </si>
-  <si>
-    <t>+23.83</t>
-  </si>
-  <si>
     <t>0.84</t>
   </si>
   <si>
@@ -338,12 +245,6 @@
     <t>PEBK</t>
   </si>
   <si>
-    <t>211.48M</t>
-  </si>
-  <si>
-    <t>+23.58</t>
-  </si>
-  <si>
     <t>-3.61</t>
   </si>
   <si>
@@ -353,12 +254,6 @@
     <t>MNSB</t>
   </si>
   <si>
-    <t>165.18M</t>
-  </si>
-  <si>
-    <t>+22.25</t>
-  </si>
-  <si>
     <t>-0.69</t>
   </si>
   <si>
@@ -371,12 +266,6 @@
     <t>HBCP</t>
   </si>
   <si>
-    <t>481.93M</t>
-  </si>
-  <si>
-    <t>+21.98</t>
-  </si>
-  <si>
     <t>-0.47</t>
   </si>
   <si>
@@ -389,12 +278,6 @@
     <t>CARE</t>
   </si>
   <si>
-    <t>572.61M</t>
-  </si>
-  <si>
-    <t>+89.36</t>
-  </si>
-  <si>
     <t>0.37</t>
   </si>
   <si>
@@ -407,12 +290,6 @@
     <t>PRAA</t>
   </si>
   <si>
-    <t>581.66M</t>
-  </si>
-  <si>
-    <t>+400.00</t>
-  </si>
-  <si>
     <t>0.99</t>
   </si>
   <si>
@@ -425,12 +302,6 @@
     <t>HAFC</t>
   </si>
   <si>
-    <t>861.91M</t>
-  </si>
-  <si>
-    <t>+18.01</t>
-  </si>
-  <si>
     <t>-4.64</t>
   </si>
   <si>
@@ -440,12 +311,6 @@
     <t>8020.SR</t>
   </si>
   <si>
-    <t>116.61M</t>
-  </si>
-  <si>
-    <t>+15.00</t>
-  </si>
-  <si>
     <t>2.00</t>
   </si>
   <si>
@@ -458,12 +323,6 @@
     <t>RMBI</t>
   </si>
   <si>
-    <t>135.69M</t>
-  </si>
-  <si>
-    <t>+12.13</t>
-  </si>
-  <si>
     <t>0.15</t>
   </si>
   <si>
@@ -476,12 +335,6 @@
     <t>TRST</t>
   </si>
   <si>
-    <t>861.79M</t>
-  </si>
-  <si>
-    <t>+11.53</t>
-  </si>
-  <si>
     <t>-3.45</t>
   </si>
   <si>
@@ -491,12 +344,6 @@
     <t>SAMG</t>
   </si>
   <si>
-    <t>92.19M</t>
-  </si>
-  <si>
-    <t>+9.83</t>
-  </si>
-  <si>
     <t>2.89</t>
   </si>
   <si>
@@ -509,264 +356,48 @@
     <t>WRLD</t>
   </si>
   <si>
-    <t>769.83M</t>
-  </si>
-  <si>
-    <t>+7.68</t>
-  </si>
-  <si>
     <t>2.40</t>
   </si>
   <si>
     <t>-2.95</t>
   </si>
   <si>
-    <t>SLM Corporation</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>4.14B</t>
-  </si>
-  <si>
-    <t>+7.65</t>
-  </si>
-  <si>
     <t>0.74</t>
   </si>
   <si>
-    <t>-5.13</t>
-  </si>
-  <si>
     <t>Amerant Bancorp Inc.</t>
   </si>
   <si>
     <t>AMTB</t>
   </si>
   <si>
-    <t>899.04M</t>
-  </si>
-  <si>
-    <t>+6.68</t>
-  </si>
-  <si>
     <t>1.77</t>
   </si>
   <si>
     <t>-5.53</t>
   </si>
   <si>
-    <t>PennyMac Financial Services, Inc.</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>4.47B</t>
-  </si>
-  <si>
-    <t>+133.99</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>-3.94</t>
-  </si>
-  <si>
-    <t>Hong Leong Financial Group Berhad</t>
-  </si>
-  <si>
-    <t>1082.KL</t>
-  </si>
-  <si>
-    <t>5.40B</t>
-  </si>
-  <si>
-    <t>+63.75</t>
-  </si>
-  <si>
-    <t>-0.53</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>-4.02</t>
-  </si>
-  <si>
-    <t>Bank OZK</t>
-  </si>
-  <si>
-    <t>OZK</t>
-  </si>
-  <si>
-    <t>5.17B</t>
-  </si>
-  <si>
-    <t>+37.90</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>-3.68</t>
-  </si>
-  <si>
     <t>Southside Bancshares, Inc.</t>
   </si>
   <si>
     <t>SBSI</t>
   </si>
   <si>
-    <t>962.88M</t>
-  </si>
-  <si>
-    <t>+37.59</t>
-  </si>
-  <si>
     <t>0.14</t>
   </si>
   <si>
     <t>-3.24</t>
   </si>
   <si>
-    <t>Fidelity National Financial, Inc.</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>12.89B</t>
-  </si>
-  <si>
-    <t>+31.78</t>
-  </si>
-  <si>
-    <t>1.06</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Zions Bancorporation, National Association</t>
-  </si>
-  <si>
-    <t>ZION</t>
-  </si>
-  <si>
-    <t>8.76B</t>
-  </si>
-  <si>
-    <t>+30.29</t>
-  </si>
-  <si>
-    <t>-0.48</t>
-  </si>
-  <si>
-    <t>-3.70</t>
-  </si>
-  <si>
-    <t>Old Republic International Corporation</t>
-  </si>
-  <si>
-    <t>ORI</t>
-  </si>
-  <si>
-    <t>9.59B</t>
-  </si>
-  <si>
-    <t>+27.72</t>
-  </si>
-  <si>
-    <t>1.53</t>
-  </si>
-  <si>
-    <t>-3.19</t>
-  </si>
-  <si>
-    <t>Japan Exchange Group, Inc.</t>
-  </si>
-  <si>
-    <t>8697.T</t>
-  </si>
-  <si>
-    <t>11.47B</t>
-  </si>
-  <si>
-    <t>+25.85</t>
-  </si>
-  <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>-2.33</t>
-  </si>
-  <si>
-    <t>Federated Hermes, Inc.</t>
-  </si>
-  <si>
-    <t>FHI</t>
-  </si>
-  <si>
-    <t>3.93B</t>
-  </si>
-  <si>
-    <t>+23.77</t>
-  </si>
-  <si>
-    <t>6.07</t>
-  </si>
-  <si>
-    <t>-3.21</t>
-  </si>
-  <si>
-    <t>Independent Bank Corporation</t>
-  </si>
-  <si>
-    <t>IBCP</t>
-  </si>
-  <si>
-    <t>673.20M</t>
-  </si>
-  <si>
-    <t>+5.23</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>South Plains Financial, Inc.</t>
-  </si>
-  <si>
-    <t>SPFI</t>
-  </si>
-  <si>
-    <t>642.63M</t>
-  </si>
-  <si>
-    <t>+2.82</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
     <t>Citizens Community Bancorp, Inc.</t>
   </si>
   <si>
     <t>CZWI</t>
   </si>
   <si>
-    <t>199.77M</t>
-  </si>
-  <si>
-    <t>-2.53</t>
-  </si>
-  <si>
     <t>1.19</t>
   </si>
   <si>
@@ -779,54 +410,18 @@
     <t>L</t>
   </si>
   <si>
-    <t>9.52M</t>
-  </si>
-  <si>
-    <t>-5.51</t>
-  </si>
-  <si>
-    <t>Red River Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>RRBI</t>
-  </si>
-  <si>
-    <t>585.42M</t>
-  </si>
-  <si>
-    <t>-6.57</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
     <t>Ames National Corporation</t>
   </si>
   <si>
     <t>ATLO</t>
   </si>
   <si>
-    <t>245.48M</t>
-  </si>
-  <si>
-    <t>-14.98</t>
-  </si>
-  <si>
-    <t>1.31</t>
-  </si>
-  <si>
-    <t>-2.61</t>
-  </si>
-  <si>
     <t>United Cooperative Assurance Company</t>
   </si>
   <si>
     <t>8190.SR</t>
   </si>
   <si>
-    <t>32.36M</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -842,9 +437,6 @@
     <t>8280.SR</t>
   </si>
   <si>
-    <t>110.69M</t>
-  </si>
-  <si>
     <t>+111.44</t>
   </si>
   <si>
@@ -863,12 +455,6 @@
     <t>INBK</t>
   </si>
   <si>
-    <t>202.36M</t>
-  </si>
-  <si>
-    <t>-65.31</t>
-  </si>
-  <si>
     <t>0.24</t>
   </si>
   <si>
@@ -878,112 +464,517 @@
     <t>FVCB</t>
   </si>
   <si>
-    <t>274.52M</t>
-  </si>
-  <si>
-    <t>+111.50</t>
-  </si>
-  <si>
     <t>-4.20</t>
   </si>
   <si>
-    <t>Green Dot Corporation</t>
-  </si>
-  <si>
-    <t>GDOT</t>
-  </si>
-  <si>
-    <t>704.03M</t>
-  </si>
-  <si>
-    <t>+109.98</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>-3.37</t>
-  </si>
-  <si>
-    <t>Employers Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>EIG</t>
-  </si>
-  <si>
-    <t>1.01B</t>
-  </si>
-  <si>
-    <t>+24.07</t>
-  </si>
-  <si>
-    <t>1.81</t>
-  </si>
-  <si>
-    <t>Amalgamated Financial Corp.</t>
-  </si>
-  <si>
-    <t>AMAL</t>
-  </si>
-  <si>
-    <t>1.18B</t>
-  </si>
-  <si>
-    <t>+19.61</t>
-  </si>
-  <si>
     <t>0.28</t>
   </si>
   <si>
     <t>-2.47</t>
   </si>
   <si>
-    <t>Heritage Financial Corporation</t>
-  </si>
-  <si>
-    <t>HFWA</t>
-  </si>
-  <si>
-    <t>+14.41</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>-2.42</t>
-  </si>
-  <si>
-    <t>Central Pacific Financial Corp.</t>
-  </si>
-  <si>
-    <t>CPF</t>
-  </si>
-  <si>
-    <t>884.25M</t>
-  </si>
-  <si>
-    <t>+5.91</t>
-  </si>
-  <si>
     <t>-2.45</t>
   </si>
   <si>
-    <t>Dime Community Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>DCOM</t>
-  </si>
-  <si>
-    <t>1.54B</t>
-  </si>
-  <si>
-    <t>+174.63</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
     <t>-2.39</t>
+  </si>
+  <si>
+    <t>113.69B</t>
+  </si>
+  <si>
+    <t>+53.04</t>
+  </si>
+  <si>
+    <t>97.84B</t>
+  </si>
+  <si>
+    <t>+55.00</t>
+  </si>
+  <si>
+    <t>377.48M</t>
+  </si>
+  <si>
+    <t>+78.50</t>
+  </si>
+  <si>
+    <t>Sumitomo Mitsui Trust Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>8309.T</t>
+  </si>
+  <si>
+    <t>25.29B</t>
+  </si>
+  <si>
+    <t>+42.03</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>-3.30</t>
+  </si>
+  <si>
+    <t>135.50M</t>
+  </si>
+  <si>
+    <t>+33.20</t>
+  </si>
+  <si>
+    <t>327.66M</t>
+  </si>
+  <si>
+    <t>+41.08</t>
+  </si>
+  <si>
+    <t>303.80M</t>
+  </si>
+  <si>
+    <t>+36.43</t>
+  </si>
+  <si>
+    <t>312.38M</t>
+  </si>
+  <si>
+    <t>+28.95</t>
+  </si>
+  <si>
+    <t>Universal Insurance Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>UVE</t>
+  </si>
+  <si>
+    <t>1.12B</t>
+  </si>
+  <si>
+    <t>+26.32</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>-2.62</t>
+  </si>
+  <si>
+    <t>423.97M</t>
+  </si>
+  <si>
+    <t>+23.33</t>
+  </si>
+  <si>
+    <t>357.52M</t>
+  </si>
+  <si>
+    <t>+23.22</t>
+  </si>
+  <si>
+    <t>332.45M</t>
+  </si>
+  <si>
+    <t>+22.95</t>
+  </si>
+  <si>
+    <t>491.21M</t>
+  </si>
+  <si>
+    <t>+19.68</t>
+  </si>
+  <si>
+    <t>168.95M</t>
+  </si>
+  <si>
+    <t>+19.52</t>
+  </si>
+  <si>
+    <t>561.13M</t>
+  </si>
+  <si>
+    <t>+418.29</t>
+  </si>
+  <si>
+    <t>583.01M</t>
+  </si>
+  <si>
+    <t>+85.98</t>
+  </si>
+  <si>
+    <t>Unity Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>UNTY</t>
+  </si>
+  <si>
+    <t>538.16M</t>
+  </si>
+  <si>
+    <t>-0.49</t>
+  </si>
+  <si>
+    <t>-2.55</t>
+  </si>
+  <si>
+    <t>114.14M</t>
+  </si>
+  <si>
+    <t>+17.67</t>
+  </si>
+  <si>
+    <t>137.38M</t>
+  </si>
+  <si>
+    <t>+10.74</t>
+  </si>
+  <si>
+    <t>Pioneer Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>PBFS</t>
+  </si>
+  <si>
+    <t>362.73M</t>
+  </si>
+  <si>
+    <t>+11.96</t>
+  </si>
+  <si>
+    <t>-0.43</t>
+  </si>
+  <si>
+    <t>92.27M</t>
+  </si>
+  <si>
+    <t>+9.74</t>
+  </si>
+  <si>
+    <t>882.63M</t>
+  </si>
+  <si>
+    <t>+8.90</t>
+  </si>
+  <si>
+    <t>902.67M</t>
+  </si>
+  <si>
+    <t>+6.25</t>
+  </si>
+  <si>
+    <t>F&amp;C Investment Trust PLC</t>
+  </si>
+  <si>
+    <t>FCIT.L</t>
+  </si>
+  <si>
+    <t>2.11B</t>
+  </si>
+  <si>
+    <t>+359.06</t>
+  </si>
+  <si>
+    <t>6.61</t>
+  </si>
+  <si>
+    <t>14.96</t>
+  </si>
+  <si>
+    <t>971.62M</t>
+  </si>
+  <si>
+    <t>+36.35</t>
+  </si>
+  <si>
+    <t>1.08B</t>
+  </si>
+  <si>
+    <t>+23.16</t>
+  </si>
+  <si>
+    <t>876.73M</t>
+  </si>
+  <si>
+    <t>+16.02</t>
+  </si>
+  <si>
+    <t>Peapack-Gladstone Financial Corporation</t>
+  </si>
+  <si>
+    <t>PGC</t>
+  </si>
+  <si>
+    <t>744.94M</t>
+  </si>
+  <si>
+    <t>+15.65</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>-2.41</t>
+  </si>
+  <si>
+    <t>785.21M</t>
+  </si>
+  <si>
+    <t>+5.58</t>
+  </si>
+  <si>
+    <t>The Bank of N.T. Butterfield &amp; Son Limited</t>
+  </si>
+  <si>
+    <t>NTB</t>
+  </si>
+  <si>
+    <t>2.23B</t>
+  </si>
+  <si>
+    <t>+0.39</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>-3.63</t>
+  </si>
+  <si>
+    <t>9.73M</t>
+  </si>
+  <si>
+    <t>-7.50</t>
+  </si>
+  <si>
+    <t>32.09M</t>
+  </si>
+  <si>
+    <t>205.73M</t>
+  </si>
+  <si>
+    <t>+215.78</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>-2.35</t>
+  </si>
+  <si>
+    <t>Hawthorn Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>HWBK</t>
+  </si>
+  <si>
+    <t>246.24M</t>
+  </si>
+  <si>
+    <t>+144.92</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>-3.35</t>
+  </si>
+  <si>
+    <t>205.39M</t>
+  </si>
+  <si>
+    <t>+35.37</t>
+  </si>
+  <si>
+    <t>First United Corporation</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>238.57M</t>
+  </si>
+  <si>
+    <t>+26.22</t>
+  </si>
+  <si>
+    <t>-0.46</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>249.50M</t>
+  </si>
+  <si>
+    <t>+24.25</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>215.27M</t>
+  </si>
+  <si>
+    <t>+21.40</t>
+  </si>
+  <si>
+    <t>199.96M</t>
+  </si>
+  <si>
+    <t>Navient Corporation</t>
+  </si>
+  <si>
+    <t>NAVI</t>
+  </si>
+  <si>
+    <t>816.84M</t>
+  </si>
+  <si>
+    <t>110.86M</t>
+  </si>
+  <si>
+    <t>277.48M</t>
+  </si>
+  <si>
+    <t>+109.24</t>
+  </si>
+  <si>
+    <t>Sound Financial Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>SFBC</t>
+  </si>
+  <si>
+    <t>108.80M</t>
+  </si>
+  <si>
+    <t>+95.46</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>11.54</t>
+  </si>
+  <si>
+    <t>Chain Bridge Bancorp, Inc.</t>
+  </si>
+  <si>
+    <t>CBNA</t>
+  </si>
+  <si>
+    <t>245.41M</t>
+  </si>
+  <si>
+    <t>+70.45</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>MetroCity Bankshares, Inc.</t>
+  </si>
+  <si>
+    <t>MCBS</t>
+  </si>
+  <si>
+    <t>932.54M</t>
+  </si>
+  <si>
+    <t>+51.06</t>
+  </si>
+  <si>
+    <t>-4.67</t>
+  </si>
+  <si>
+    <t>Beacon Financial Corp.</t>
+  </si>
+  <si>
+    <t>BBT</t>
+  </si>
+  <si>
+    <t>2.36B</t>
+  </si>
+  <si>
+    <t>+39.87</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>-3.51</t>
+  </si>
+  <si>
+    <t>Bank of Hawaii Corporation</t>
+  </si>
+  <si>
+    <t>BOH</t>
+  </si>
+  <si>
+    <t>3.02B</t>
+  </si>
+  <si>
+    <t>+34.91</t>
+  </si>
+  <si>
+    <t>-2.46</t>
+  </si>
+  <si>
+    <t>BankUnited, Inc.</t>
+  </si>
+  <si>
+    <t>BKU</t>
+  </si>
+  <si>
+    <t>3.46B</t>
+  </si>
+  <si>
+    <t>+34.72</t>
+  </si>
+  <si>
+    <t>3.88B</t>
+  </si>
+  <si>
+    <t>+33.16</t>
+  </si>
+  <si>
+    <t>Eagle Bancorp Montana, Inc.</t>
+  </si>
+  <si>
+    <t>EBMT</t>
+  </si>
+  <si>
+    <t>170.53M</t>
+  </si>
+  <si>
+    <t>+32.69</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Banner Corporation</t>
+  </si>
+  <si>
+    <t>BANR</t>
+  </si>
+  <si>
+    <t>2.18B</t>
+  </si>
+  <si>
+    <t>+25.50</t>
+  </si>
+  <si>
+    <t>-2.13</t>
+  </si>
+  <si>
+    <t>Cathay General Bancorp</t>
+  </si>
+  <si>
+    <t>CATY</t>
+  </si>
+  <si>
+    <t>3.78B</t>
+  </si>
+  <si>
+    <t>+18.54</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1390,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1408,22 +1399,22 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1433,36 +1424,36 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1470,33 +1461,33 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1504,33 +1495,33 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1538,33 +1529,33 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1572,33 +1563,33 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,33 +1597,33 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1640,33 +1631,33 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1674,33 +1665,33 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,33 +1699,33 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,33 +1733,33 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1776,33 +1767,33 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1810,33 +1801,33 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1844,33 +1835,33 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1878,33 +1869,33 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1912,33 +1903,33 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1946,33 +1937,33 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1980,33 +1971,33 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="F36" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2014,33 +2005,33 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="F38" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H38" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2048,33 +2039,33 @@
         <v>18</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2082,33 +2073,33 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H42" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2116,33 +2107,33 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H44" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2150,33 +2141,33 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="E46" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H46" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2184,33 +2175,33 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="E48" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="F48" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2218,33 +2209,33 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="F50" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2252,33 +2243,33 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="E52" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="F52" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2286,33 +2277,33 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2320,33 +2311,33 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="D56" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="E56" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="F56" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>32</v>
       </c>
       <c r="H56" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2354,33 +2345,33 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="E58" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="F58" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="G58" t="s">
-        <v>185</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2388,33 +2379,33 @@
         <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="C60" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="D60" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F60" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="G60" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H60" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2422,33 +2413,33 @@
         <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="F62" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2456,33 +2447,33 @@
         <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D64" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="E64" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="H64" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2490,33 +2481,33 @@
         <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="E66" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="F66" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="G66" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="H66" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2524,33 +2515,33 @@
         <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="C68" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="F68" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="G68" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H68" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2558,33 +2549,33 @@
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>217</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="F70" t="s">
-        <v>221</v>
+        <v>40</v>
       </c>
       <c r="G70" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H70" t="s">
-        <v>222</v>
+        <v>41</v>
       </c>
       <c r="I70" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2592,33 +2583,33 @@
         <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C72" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="D72" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="E72" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="F72" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="G72" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H72" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="I72" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2626,33 +2617,33 @@
         <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="C74" t="s">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="D74" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F74" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="G74" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H74" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>230</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2660,33 +2651,33 @@
         <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="C76" t="s">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="E76" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="F76" t="s">
-        <v>238</v>
+        <v>61</v>
       </c>
       <c r="G76" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H76" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2694,33 +2685,33 @@
         <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="F78" t="s">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="G78" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H78" t="s">
-        <v>244</v>
+        <v>121</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2728,33 +2719,33 @@
         <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="I80" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -2762,33 +2753,33 @@
         <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="C82" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="F82" t="s">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="G82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="I82" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2796,33 +2787,33 @@
         <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="C84" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="D84" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E84" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F84" t="s">
-        <v>258</v>
+        <v>139</v>
       </c>
       <c r="G84" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H84" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="I84" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2830,33 +2821,33 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E86" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F86" t="s">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="G86" t="s">
-        <v>264</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I86" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2864,33 +2855,33 @@
         <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D88" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E88" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F88" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="H88" t="s">
-        <v>271</v>
+        <v>92</v>
       </c>
       <c r="I88" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -2898,33 +2889,33 @@
         <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C90" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D90" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E90" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F90" t="s">
-        <v>277</v>
+        <v>40</v>
       </c>
       <c r="G90" t="s">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>108</v>
+        <v>281</v>
       </c>
       <c r="I90" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -2932,33 +2923,33 @@
         <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C92" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E92" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F92" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="G92" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="H92" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I92" t="s">
-        <v>272</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -2966,33 +2957,33 @@
         <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E94" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F94" t="s">
-        <v>287</v>
+        <v>61</v>
       </c>
       <c r="G94" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="H94" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I94" t="s">
-        <v>272</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3000,33 +2991,33 @@
         <v>46</v>
       </c>
       <c r="B96" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C96" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D96" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E96" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F96" t="s">
-        <v>293</v>
+        <v>223</v>
       </c>
       <c r="G96" t="s">
-        <v>263</v>
+        <v>28</v>
       </c>
       <c r="H96" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="I96" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3034,33 +3025,33 @@
         <v>47</v>
       </c>
       <c r="B98" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F98" t="s">
-        <v>298</v>
+        <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H98" t="s">
-        <v>299</v>
+        <v>29</v>
       </c>
       <c r="I98" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>295</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -3068,13 +3059,13 @@
         <v>48</v>
       </c>
       <c r="B100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D100" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="E100" t="s">
         <v>302</v>
@@ -3083,18 +3074,18 @@
         <v>303</v>
       </c>
       <c r="G100" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H100" t="s">
-        <v>304</v>
+        <v>144</v>
       </c>
       <c r="I100" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -3102,33 +3093,33 @@
         <v>49</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D102" t="s">
+        <v>306</v>
+      </c>
+      <c r="E102" t="s">
         <v>307</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>143</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
         <v>308</v>
       </c>
-      <c r="F102" t="s">
-        <v>233</v>
-      </c>
-      <c r="G102" t="s">
-        <v>28</v>
-      </c>
-      <c r="H102" t="s">
-        <v>309</v>
-      </c>
       <c r="I102" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -3136,33 +3127,33 @@
         <v>50</v>
       </c>
       <c r="B104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D104" t="s">
+        <v>311</v>
+      </c>
+      <c r="E104" t="s">
         <v>312</v>
       </c>
-      <c r="E104" t="s">
-        <v>313</v>
-      </c>
       <c r="F104" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="G104" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H104" t="s">
-        <v>315</v>
+        <v>145</v>
       </c>
       <c r="I104" t="s">
-        <v>272</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_fin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DAFEE75-A5EC-4253-BE25-917B951D994E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{12D6B79E-6030-4470-918D-496C823CB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26BDA85-5D26-4FCF-BDF3-37667C24B9D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CD7A04BB-561F-44B5-BA10-41E0FF983FF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="308">
   <si>
     <t>Symbol</t>
   </si>
@@ -62,39 +62,18 @@
     <t>Value Generation</t>
   </si>
   <si>
-    <t>BNP Paribas S.A.</t>
-  </si>
-  <si>
-    <t>BNP.PA</t>
-  </si>
-  <si>
-    <t>-0.14</t>
-  </si>
-  <si>
     <t>6.0</t>
   </si>
   <si>
-    <t>-2.18</t>
-  </si>
-  <si>
     <t>Steady</t>
   </si>
   <si>
-    <t>AXA S.A.</t>
-  </si>
-  <si>
-    <t>CS.PA</t>
-  </si>
-  <si>
     <t>0.36</t>
   </si>
   <si>
     <t>5.0</t>
   </si>
   <si>
-    <t>-1.37</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
@@ -113,21 +92,9 @@
     <t>-3.53</t>
   </si>
   <si>
-    <t>Quálitas Controladora, S.A.B. de C.V.</t>
-  </si>
-  <si>
-    <t>Q.MX</t>
-  </si>
-  <si>
-    <t>1.56</t>
-  </si>
-  <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>-7.14</t>
-  </si>
-  <si>
     <t>SB Financial Group, Inc.</t>
   </si>
   <si>
@@ -218,9 +185,6 @@
     <t>PKBK</t>
   </si>
   <si>
-    <t>+25.02</t>
-  </si>
-  <si>
     <t>0.32</t>
   </si>
   <si>
@@ -350,18 +314,6 @@
     <t>-1.48</t>
   </si>
   <si>
-    <t>World Acceptance Corporation</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>2.40</t>
-  </si>
-  <si>
-    <t>-2.95</t>
-  </si>
-  <si>
     <t>0.74</t>
   </si>
   <si>
@@ -380,18 +332,6 @@
     <t>3.0</t>
   </si>
   <si>
-    <t>Southside Bancshares, Inc.</t>
-  </si>
-  <si>
-    <t>SBSI</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>-3.24</t>
-  </si>
-  <si>
     <t>Citizens Community Bancorp, Inc.</t>
   </si>
   <si>
@@ -431,21 +371,6 @@
     <t>-3.90</t>
   </si>
   <si>
-    <t>Al Alamiya for Cooperative Insurance Company</t>
-  </si>
-  <si>
-    <t>8280.SR</t>
-  </si>
-  <si>
-    <t>+111.44</t>
-  </si>
-  <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>-3.34</t>
-  </si>
-  <si>
     <t>Resilient</t>
   </si>
   <si>
@@ -455,303 +380,48 @@
     <t>INBK</t>
   </si>
   <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>FVCBankcorp, Inc.</t>
-  </si>
-  <si>
-    <t>FVCB</t>
-  </si>
-  <si>
-    <t>-4.20</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>-2.47</t>
-  </si>
-  <si>
     <t>-2.45</t>
   </si>
   <si>
     <t>-2.39</t>
   </si>
   <si>
-    <t>113.69B</t>
-  </si>
-  <si>
-    <t>+53.04</t>
-  </si>
-  <si>
-    <t>97.84B</t>
-  </si>
-  <si>
-    <t>+55.00</t>
-  </si>
-  <si>
-    <t>377.48M</t>
-  </si>
-  <si>
-    <t>+78.50</t>
-  </si>
-  <si>
-    <t>Sumitomo Mitsui Trust Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>8309.T</t>
-  </si>
-  <si>
-    <t>25.29B</t>
-  </si>
-  <si>
-    <t>+42.03</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>-3.30</t>
-  </si>
-  <si>
-    <t>135.50M</t>
-  </si>
-  <si>
-    <t>+33.20</t>
-  </si>
-  <si>
-    <t>327.66M</t>
-  </si>
-  <si>
-    <t>+41.08</t>
-  </si>
-  <si>
-    <t>303.80M</t>
-  </si>
-  <si>
-    <t>+36.43</t>
-  </si>
-  <si>
-    <t>312.38M</t>
-  </si>
-  <si>
-    <t>+28.95</t>
-  </si>
-  <si>
     <t>Universal Insurance Holdings, Inc.</t>
   </si>
   <si>
     <t>UVE</t>
   </si>
   <si>
-    <t>1.12B</t>
-  </si>
-  <si>
-    <t>+26.32</t>
-  </si>
-  <si>
     <t>1.16</t>
   </si>
   <si>
     <t>-2.62</t>
   </si>
   <si>
-    <t>423.97M</t>
-  </si>
-  <si>
-    <t>+23.33</t>
-  </si>
-  <si>
-    <t>357.52M</t>
-  </si>
-  <si>
-    <t>+23.22</t>
-  </si>
-  <si>
-    <t>332.45M</t>
-  </si>
-  <si>
-    <t>+22.95</t>
-  </si>
-  <si>
-    <t>491.21M</t>
-  </si>
-  <si>
-    <t>+19.68</t>
-  </si>
-  <si>
-    <t>168.95M</t>
-  </si>
-  <si>
-    <t>+19.52</t>
-  </si>
-  <si>
-    <t>561.13M</t>
-  </si>
-  <si>
-    <t>+418.29</t>
-  </si>
-  <si>
-    <t>583.01M</t>
-  </si>
-  <si>
-    <t>+85.98</t>
-  </si>
-  <si>
     <t>Unity Bancorp, Inc.</t>
   </si>
   <si>
     <t>UNTY</t>
   </si>
   <si>
-    <t>538.16M</t>
-  </si>
-  <si>
     <t>-0.49</t>
   </si>
   <si>
     <t>-2.55</t>
   </si>
   <si>
-    <t>114.14M</t>
-  </si>
-  <si>
-    <t>+17.67</t>
-  </si>
-  <si>
-    <t>137.38M</t>
-  </si>
-  <si>
-    <t>+10.74</t>
-  </si>
-  <si>
-    <t>Pioneer Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>PBFS</t>
-  </si>
-  <si>
-    <t>362.73M</t>
-  </si>
-  <si>
-    <t>+11.96</t>
-  </si>
-  <si>
-    <t>-0.43</t>
-  </si>
-  <si>
-    <t>92.27M</t>
-  </si>
-  <si>
-    <t>+9.74</t>
-  </si>
-  <si>
-    <t>882.63M</t>
-  </si>
-  <si>
-    <t>+8.90</t>
-  </si>
-  <si>
-    <t>902.67M</t>
-  </si>
-  <si>
-    <t>+6.25</t>
-  </si>
-  <si>
     <t>F&amp;C Investment Trust PLC</t>
   </si>
   <si>
     <t>FCIT.L</t>
   </si>
   <si>
-    <t>2.11B</t>
-  </si>
-  <si>
-    <t>+359.06</t>
-  </si>
-  <si>
     <t>6.61</t>
   </si>
   <si>
     <t>14.96</t>
   </si>
   <si>
-    <t>971.62M</t>
-  </si>
-  <si>
-    <t>+36.35</t>
-  </si>
-  <si>
-    <t>1.08B</t>
-  </si>
-  <si>
-    <t>+23.16</t>
-  </si>
-  <si>
-    <t>876.73M</t>
-  </si>
-  <si>
-    <t>+16.02</t>
-  </si>
-  <si>
-    <t>Peapack-Gladstone Financial Corporation</t>
-  </si>
-  <si>
-    <t>PGC</t>
-  </si>
-  <si>
-    <t>744.94M</t>
-  </si>
-  <si>
-    <t>+15.65</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>-2.41</t>
-  </si>
-  <si>
-    <t>785.21M</t>
-  </si>
-  <si>
-    <t>+5.58</t>
-  </si>
-  <si>
-    <t>The Bank of N.T. Butterfield &amp; Son Limited</t>
-  </si>
-  <si>
-    <t>NTB</t>
-  </si>
-  <si>
-    <t>2.23B</t>
-  </si>
-  <si>
-    <t>+0.39</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>-3.63</t>
-  </si>
-  <si>
-    <t>9.73M</t>
-  </si>
-  <si>
-    <t>-7.50</t>
-  </si>
-  <si>
-    <t>32.09M</t>
-  </si>
-  <si>
-    <t>205.73M</t>
-  </si>
-  <si>
-    <t>+215.78</t>
-  </si>
-  <si>
     <t>0.10</t>
   </si>
   <si>
@@ -764,217 +434,532 @@
     <t>HWBK</t>
   </si>
   <si>
-    <t>246.24M</t>
-  </si>
-  <si>
-    <t>+144.92</t>
-  </si>
-  <si>
     <t>0.30</t>
   </si>
   <si>
     <t>-3.35</t>
   </si>
   <si>
-    <t>205.39M</t>
-  </si>
-  <si>
-    <t>+35.37</t>
-  </si>
-  <si>
     <t>First United Corporation</t>
   </si>
   <si>
     <t>FUNC</t>
   </si>
   <si>
-    <t>238.57M</t>
-  </si>
-  <si>
-    <t>+26.22</t>
-  </si>
-  <si>
     <t>-0.46</t>
   </si>
   <si>
     <t>0.54</t>
   </si>
   <si>
-    <t>249.50M</t>
-  </si>
-  <si>
-    <t>+24.25</t>
-  </si>
-  <si>
     <t>1.38</t>
   </si>
   <si>
-    <t>215.27M</t>
-  </si>
-  <si>
-    <t>+21.40</t>
-  </si>
-  <si>
-    <t>199.96M</t>
-  </si>
-  <si>
-    <t>Navient Corporation</t>
-  </si>
-  <si>
-    <t>NAVI</t>
-  </si>
-  <si>
-    <t>816.84M</t>
-  </si>
-  <si>
-    <t>110.86M</t>
-  </si>
-  <si>
-    <t>277.48M</t>
-  </si>
-  <si>
-    <t>+109.24</t>
-  </si>
-  <si>
-    <t>Sound Financial Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>SFBC</t>
-  </si>
-  <si>
-    <t>108.80M</t>
-  </si>
-  <si>
-    <t>+95.46</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>11.54</t>
-  </si>
-  <si>
-    <t>Chain Bridge Bancorp, Inc.</t>
-  </si>
-  <si>
-    <t>CBNA</t>
-  </si>
-  <si>
-    <t>245.41M</t>
-  </si>
-  <si>
-    <t>+70.45</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>MetroCity Bankshares, Inc.</t>
-  </si>
-  <si>
-    <t>MCBS</t>
-  </si>
-  <si>
-    <t>932.54M</t>
-  </si>
-  <si>
-    <t>+51.06</t>
-  </si>
-  <si>
-    <t>-4.67</t>
-  </si>
-  <si>
-    <t>Beacon Financial Corp.</t>
-  </si>
-  <si>
-    <t>BBT</t>
-  </si>
-  <si>
-    <t>2.36B</t>
-  </si>
-  <si>
-    <t>+39.87</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>-3.51</t>
-  </si>
-  <si>
-    <t>Bank of Hawaii Corporation</t>
-  </si>
-  <si>
-    <t>BOH</t>
-  </si>
-  <si>
-    <t>3.02B</t>
-  </si>
-  <si>
-    <t>+34.91</t>
-  </si>
-  <si>
     <t>-2.46</t>
   </si>
   <si>
-    <t>BankUnited, Inc.</t>
-  </si>
-  <si>
-    <t>BKU</t>
-  </si>
-  <si>
-    <t>3.46B</t>
-  </si>
-  <si>
-    <t>+34.72</t>
-  </si>
-  <si>
-    <t>3.88B</t>
-  </si>
-  <si>
-    <t>+33.16</t>
-  </si>
-  <si>
-    <t>Eagle Bancorp Montana, Inc.</t>
-  </si>
-  <si>
-    <t>EBMT</t>
-  </si>
-  <si>
-    <t>170.53M</t>
-  </si>
-  <si>
-    <t>+32.69</t>
-  </si>
-  <si>
     <t>0.40</t>
   </si>
   <si>
-    <t>Banner Corporation</t>
-  </si>
-  <si>
-    <t>BANR</t>
-  </si>
-  <si>
-    <t>2.18B</t>
-  </si>
-  <si>
-    <t>+25.50</t>
-  </si>
-  <si>
-    <t>-2.13</t>
-  </si>
-  <si>
     <t>Cathay General Bancorp</t>
   </si>
   <si>
     <t>CATY</t>
   </si>
   <si>
-    <t>3.78B</t>
-  </si>
-  <si>
-    <t>+18.54</t>
+    <t>PayPal Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>PYPL</t>
+  </si>
+  <si>
+    <t>40.86B</t>
+  </si>
+  <si>
+    <t>+94.19</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>52.96</t>
+  </si>
+  <si>
+    <t>382.74M</t>
+  </si>
+  <si>
+    <t>+75.77</t>
+  </si>
+  <si>
+    <t>1.03B</t>
+  </si>
+  <si>
+    <t>+36.79</t>
+  </si>
+  <si>
+    <t>134.57M</t>
+  </si>
+  <si>
+    <t>+34.12</t>
+  </si>
+  <si>
+    <t>FactSet Research Systems Inc.</t>
+  </si>
+  <si>
+    <t>FDS</t>
+  </si>
+  <si>
+    <t>9.06B</t>
+  </si>
+  <si>
+    <t>+65.82</t>
+  </si>
+  <si>
+    <t>4.38</t>
+  </si>
+  <si>
+    <t>The Company for Cooperative Insurance</t>
+  </si>
+  <si>
+    <t>8010.SR</t>
+  </si>
+  <si>
+    <t>5.49B</t>
+  </si>
+  <si>
+    <t>+47.09</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>-3.49</t>
+  </si>
+  <si>
+    <t>320.31M</t>
+  </si>
+  <si>
+    <t>+44.32</t>
+  </si>
+  <si>
+    <t>306.06M</t>
+  </si>
+  <si>
+    <t>+35.42</t>
+  </si>
+  <si>
+    <t>319.59M</t>
+  </si>
+  <si>
+    <t>+26.05</t>
+  </si>
+  <si>
+    <t>359.74M</t>
+  </si>
+  <si>
+    <t>+22.45</t>
+  </si>
+  <si>
+    <t>336.00M</t>
+  </si>
+  <si>
+    <t>+21.66</t>
+  </si>
+  <si>
+    <t>113.29M</t>
+  </si>
+  <si>
+    <t>+18.36</t>
+  </si>
+  <si>
+    <t>497.46M</t>
+  </si>
+  <si>
+    <t>+18.17</t>
+  </si>
+  <si>
+    <t>171.32M</t>
+  </si>
+  <si>
+    <t>+17.87</t>
+  </si>
+  <si>
+    <t>210.88M</t>
+  </si>
+  <si>
+    <t>+208.07</t>
+  </si>
+  <si>
+    <t>253.67M</t>
+  </si>
+  <si>
+    <t>+137.75</t>
+  </si>
+  <si>
+    <t>212.36M</t>
+  </si>
+  <si>
+    <t>+30.92</t>
+  </si>
+  <si>
+    <t>256.46M</t>
+  </si>
+  <si>
+    <t>+20.88</t>
+  </si>
+  <si>
+    <t>256.34M</t>
+  </si>
+  <si>
+    <t>+17.48</t>
+  </si>
+  <si>
+    <t>223.09M</t>
+  </si>
+  <si>
+    <t>+17.15</t>
+  </si>
+  <si>
+    <t>446.78M</t>
+  </si>
+  <si>
+    <t>+17.04</t>
+  </si>
+  <si>
+    <t>87.05M</t>
+  </si>
+  <si>
+    <t>+16.33</t>
+  </si>
+  <si>
+    <t>Independent Bank Corporation</t>
+  </si>
+  <si>
+    <t>IBCP</t>
+  </si>
+  <si>
+    <t>706.12M</t>
+  </si>
+  <si>
+    <t>+15.06</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>-3.57</t>
+  </si>
+  <si>
+    <t>892.43M</t>
+  </si>
+  <si>
+    <t>+13.98</t>
+  </si>
+  <si>
+    <t>Capitol Federal Financial, Inc.</t>
+  </si>
+  <si>
+    <t>CFFN</t>
+  </si>
+  <si>
+    <t>983.92M</t>
+  </si>
+  <si>
+    <t>+48.52</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>-0.90</t>
+  </si>
+  <si>
+    <t>1.11B</t>
+  </si>
+  <si>
+    <t>+20.79</t>
+  </si>
+  <si>
+    <t>Heritage Financial Corporation</t>
+  </si>
+  <si>
+    <t>HFWA</t>
+  </si>
+  <si>
+    <t>1.05B</t>
+  </si>
+  <si>
+    <t>+18.53</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>-3.42</t>
+  </si>
+  <si>
+    <t>3.87B</t>
+  </si>
+  <si>
+    <t>+15.83</t>
+  </si>
+  <si>
+    <t>140.52M</t>
+  </si>
+  <si>
+    <t>+8.26</t>
+  </si>
+  <si>
+    <t>915.97M</t>
+  </si>
+  <si>
+    <t>+4.71</t>
+  </si>
+  <si>
+    <t>922.89M</t>
+  </si>
+  <si>
+    <t>+4.15</t>
+  </si>
+  <si>
+    <t>First Business Financial Services, Inc.</t>
+  </si>
+  <si>
+    <t>FBIZ</t>
+  </si>
+  <si>
+    <t>470.87M</t>
+  </si>
+  <si>
+    <t>+4.00</t>
+  </si>
+  <si>
+    <t>1.28</t>
+  </si>
+  <si>
+    <t>-3.17</t>
+  </si>
+  <si>
+    <t>2.19B</t>
+  </si>
+  <si>
+    <t>+344.03</t>
+  </si>
+  <si>
+    <t>198.02M</t>
+  </si>
+  <si>
+    <t>-1.67</t>
+  </si>
+  <si>
+    <t>585.50M</t>
+  </si>
+  <si>
+    <t>+396.72</t>
+  </si>
+  <si>
+    <t>596.42M</t>
+  </si>
+  <si>
+    <t>+81.79</t>
+  </si>
+  <si>
+    <t>559.27M</t>
+  </si>
+  <si>
+    <t>+20.30</t>
+  </si>
+  <si>
+    <t>9.32M</t>
+  </si>
+  <si>
+    <t>-3.46</t>
+  </si>
+  <si>
+    <t>32.14M</t>
+  </si>
+  <si>
+    <t>Dime Community Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>DCOM</t>
+  </si>
+  <si>
+    <t>1.61B</t>
+  </si>
+  <si>
+    <t>+162.08</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Encore Capital Group, Inc.</t>
+  </si>
+  <si>
+    <t>ECPG</t>
+  </si>
+  <si>
+    <t>1.74B</t>
+  </si>
+  <si>
+    <t>+68.40</t>
+  </si>
+  <si>
+    <t>1.99</t>
+  </si>
+  <si>
+    <t>-2.32</t>
+  </si>
+  <si>
+    <t>SLM Corporation</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>4.32B</t>
+  </si>
+  <si>
+    <t>+3.03</t>
+  </si>
+  <si>
+    <t>-5.13</t>
+  </si>
+  <si>
+    <t>PennyMac Financial Services, Inc.</t>
+  </si>
+  <si>
+    <t>PFSI</t>
+  </si>
+  <si>
+    <t>4.37B</t>
+  </si>
+  <si>
+    <t>+139.07</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>-3.94</t>
+  </si>
+  <si>
+    <t>Bupa Arabia for Cooperative Insurance Company</t>
+  </si>
+  <si>
+    <t>8210.SR</t>
+  </si>
+  <si>
+    <t>6.78B</t>
+  </si>
+  <si>
+    <t>+30.16</t>
+  </si>
+  <si>
+    <t>2.88</t>
+  </si>
+  <si>
+    <t>-3.40</t>
+  </si>
+  <si>
+    <t>Morningstar, Inc.</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>7.12B</t>
+  </si>
+  <si>
+    <t>+120.89</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>-2.51</t>
+  </si>
+  <si>
+    <t>First American Financial Corporation</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>6.82B</t>
+  </si>
+  <si>
+    <t>+68.13</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>Bank AlJazira</t>
+  </si>
+  <si>
+    <t>1020.SR</t>
+  </si>
+  <si>
+    <t>+62.37</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>-5.17</t>
+  </si>
+  <si>
+    <t>Jackson Financial Inc.</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>7.23B</t>
+  </si>
+  <si>
+    <t>+33.17</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>Commerce Bancshares, Inc.</t>
+  </si>
+  <si>
+    <t>CBSH</t>
+  </si>
+  <si>
+    <t>7.62B</t>
+  </si>
+  <si>
+    <t>+23.78</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>-3.38</t>
+  </si>
+  <si>
+    <t>Banca Generali S.p.A.</t>
+  </si>
+  <si>
+    <t>BGN.MI</t>
+  </si>
+  <si>
+    <t>7.45B</t>
+  </si>
+  <si>
+    <t>+19.65</t>
+  </si>
+  <si>
+    <t>-0.53</t>
+  </si>
+  <si>
+    <t>-3.88</t>
   </si>
 </sst>
 </file>
@@ -1350,11 +1335,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815B5833-788F-4279-8BDF-C70713B76FD4}">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1390,28 +1375,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>148</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1419,12 +1404,12 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1442,10 +1427,10 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
         <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -1458,13 +1443,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>151</v>
@@ -1473,1687 +1458,1619 @@
         <v>152</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
         <v>153</v>
       </c>
-      <c r="C8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" t="s">
-        <v>155</v>
-      </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F8" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" t="s">
         <v>159</v>
       </c>
-      <c r="E10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" t="s">
         <v>173</v>
       </c>
-      <c r="E20" t="s">
-        <v>174</v>
-      </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" t="s">
         <v>175</v>
       </c>
-      <c r="E22" t="s">
-        <v>176</v>
-      </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" t="s">
         <v>177</v>
       </c>
-      <c r="E24" t="s">
-        <v>178</v>
-      </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" t="s">
         <v>179</v>
       </c>
-      <c r="E26" t="s">
-        <v>180</v>
-      </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" t="s">
         <v>181</v>
       </c>
-      <c r="E28" t="s">
-        <v>182</v>
-      </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" t="s">
         <v>183</v>
       </c>
-      <c r="E30" t="s">
-        <v>184</v>
-      </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="H30" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" t="s">
         <v>185</v>
       </c>
-      <c r="E32" t="s">
-        <v>186</v>
-      </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" t="s">
         <v>187</v>
       </c>
-      <c r="C34" t="s">
-        <v>187</v>
-      </c>
-      <c r="D34" t="s">
-        <v>189</v>
-      </c>
-      <c r="E34" t="s">
-        <v>60</v>
-      </c>
       <c r="F34" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" t="s">
         <v>18</v>
       </c>
-      <c r="B40" t="s">
-        <v>196</v>
-      </c>
-      <c r="C40" t="s">
-        <v>196</v>
-      </c>
-      <c r="D40" t="s">
-        <v>198</v>
-      </c>
-      <c r="E40" t="s">
-        <v>199</v>
-      </c>
-      <c r="F40" t="s">
-        <v>200</v>
-      </c>
-      <c r="G40" t="s">
-        <v>17</v>
-      </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E46" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>110</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E48" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F48" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>208</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="D50" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E50" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>115</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F52" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="D54" t="s">
+        <v>216</v>
+      </c>
+      <c r="E54" t="s">
         <v>217</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>218</v>
       </c>
-      <c r="F54" t="s">
-        <v>44</v>
-      </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="I54" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>87</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>219</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>219</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56" t="s">
         <v>221</v>
       </c>
-      <c r="E56" t="s">
-        <v>222</v>
-      </c>
       <c r="F56" t="s">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>224</v>
+        <v>114</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E58" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H58" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E60" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F60" t="s">
-        <v>231</v>
+        <v>95</v>
       </c>
       <c r="G60" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>232</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>228</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
+        <v>31</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
+        <v>85</v>
+      </c>
+      <c r="D62" t="s">
+        <v>226</v>
+      </c>
+      <c r="E62" t="s">
+        <v>227</v>
+      </c>
+      <c r="F62" t="s">
         <v>29</v>
       </c>
-      <c r="B62" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" t="s">
-        <v>233</v>
-      </c>
-      <c r="E62" t="s">
-        <v>234</v>
-      </c>
-      <c r="F62" t="s">
-        <v>108</v>
-      </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="D64" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="F64" t="s">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="G64" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E66" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F66" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="H66" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>240</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>240</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E68" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F68" t="s">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H68" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>241</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D70" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E70" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="F70" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G70" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="D72" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E72" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="F72" t="s">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="G72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H72" t="s">
-        <v>253</v>
+        <v>69</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>249</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D74" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E74" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F74" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C76" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D76" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E76" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="F76" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="G76" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D78" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="E78" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="F78" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="G78" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="H78" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C80" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D80" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="E80" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F80" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H80" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="D82" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E82" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="F82" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="G82" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="I82" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>132</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="D84" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E84" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="G84" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H84" t="s">
-        <v>142</v>
+        <v>262</v>
       </c>
       <c r="I84" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
+        <v>263</v>
+      </c>
+      <c r="C86" t="s">
+        <v>263</v>
+      </c>
+      <c r="D86" t="s">
+        <v>265</v>
+      </c>
+      <c r="E86" t="s">
         <v>266</v>
       </c>
-      <c r="C86" t="s">
-        <v>266</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="F86" t="s">
+        <v>267</v>
+      </c>
+      <c r="G86" t="s">
+        <v>97</v>
+      </c>
+      <c r="H86" t="s">
         <v>268</v>
       </c>
-      <c r="E86" t="s">
-        <v>269</v>
-      </c>
-      <c r="F86" t="s">
-        <v>270</v>
-      </c>
-      <c r="G86" t="s">
-        <v>28</v>
-      </c>
-      <c r="H86" t="s">
-        <v>271</v>
-      </c>
       <c r="I86" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
+        <v>269</v>
+      </c>
+      <c r="C88" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" t="s">
+        <v>271</v>
+      </c>
+      <c r="E88" t="s">
         <v>272</v>
       </c>
-      <c r="C88" t="s">
-        <v>272</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
+        <v>273</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" t="s">
         <v>274</v>
       </c>
-      <c r="E88" t="s">
-        <v>275</v>
-      </c>
-      <c r="F88" t="s">
-        <v>276</v>
-      </c>
-      <c r="G88" t="s">
-        <v>129</v>
-      </c>
-      <c r="H88" t="s">
-        <v>92</v>
-      </c>
       <c r="I88" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
+        <v>275</v>
+      </c>
+      <c r="C90" t="s">
+        <v>275</v>
+      </c>
+      <c r="D90" t="s">
         <v>277</v>
       </c>
-      <c r="C90" t="s">
-        <v>277</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
+        <v>278</v>
+      </c>
+      <c r="F90" t="s">
         <v>279</v>
-      </c>
-      <c r="E90" t="s">
-        <v>280</v>
-      </c>
-      <c r="F90" t="s">
-        <v>40</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I90" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C92" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D92" t="s">
+        <v>283</v>
+      </c>
+      <c r="E92" t="s">
         <v>284</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>285</v>
       </c>
-      <c r="F92" t="s">
-        <v>286</v>
-      </c>
       <c r="G92" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H92" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="I92" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B94" t="s">
+        <v>286</v>
+      </c>
+      <c r="C94" t="s">
+        <v>286</v>
+      </c>
+      <c r="D94" t="s">
+        <v>220</v>
+      </c>
+      <c r="E94" t="s">
         <v>288</v>
       </c>
-      <c r="C94" t="s">
-        <v>288</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
+        <v>289</v>
+      </c>
+      <c r="G94" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94" t="s">
         <v>290</v>
       </c>
-      <c r="E94" t="s">
-        <v>291</v>
-      </c>
-      <c r="F94" t="s">
-        <v>61</v>
-      </c>
-      <c r="G94" t="s">
-        <v>19</v>
-      </c>
-      <c r="H94" t="s">
-        <v>292</v>
-      </c>
       <c r="I94" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B96" t="s">
+        <v>291</v>
+      </c>
+      <c r="C96" t="s">
+        <v>291</v>
+      </c>
+      <c r="D96" t="s">
         <v>293</v>
       </c>
-      <c r="C96" t="s">
-        <v>293</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>294</v>
+      </c>
+      <c r="F96" t="s">
         <v>295</v>
       </c>
-      <c r="E96" t="s">
-        <v>296</v>
-      </c>
-      <c r="F96" t="s">
-        <v>223</v>
-      </c>
       <c r="G96" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="H96" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I96" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
+        <v>296</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>296</v>
       </c>
       <c r="D98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>300</v>
       </c>
       <c r="G98" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="I98" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>26</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C100" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D100" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E100" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F100" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G100" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="H100" t="s">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="I100" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>49</v>
-      </c>
-      <c r="B102" t="s">
-        <v>304</v>
-      </c>
-      <c r="C102" t="s">
-        <v>304</v>
-      </c>
-      <c r="D102" t="s">
-        <v>306</v>
-      </c>
-      <c r="E102" t="s">
-        <v>307</v>
-      </c>
-      <c r="F102" t="s">
-        <v>143</v>
-      </c>
-      <c r="G102" t="s">
-        <v>19</v>
-      </c>
-      <c r="H102" t="s">
-        <v>308</v>
-      </c>
-      <c r="I102" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>50</v>
-      </c>
-      <c r="B104" t="s">
-        <v>309</v>
-      </c>
-      <c r="C104" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" t="s">
-        <v>311</v>
-      </c>
-      <c r="E104" t="s">
-        <v>312</v>
-      </c>
-      <c r="F104" t="s">
         <v>303</v>
-      </c>
-      <c r="G104" t="s">
-        <v>19</v>
-      </c>
-      <c r="H104" t="s">
-        <v>145</v>
-      </c>
-      <c r="I104" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
